--- a/research/traditional_assets/database/data/luxembourg/luxembourg_software_entertainment.xlsx
+++ b/research/traditional_assets/database/data/luxembourg/luxembourg_software_entertainment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtpa_aldnx" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,43 +590,43 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.159</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="G2">
-        <v>0.1696069868995633</v>
+        <v>0.2206572769953052</v>
       </c>
       <c r="H2">
-        <v>0.1689956331877729</v>
+        <v>0.2206572769953052</v>
       </c>
       <c r="I2">
-        <v>0.1746724890829695</v>
+        <v>0.212206572769953</v>
       </c>
       <c r="J2">
-        <v>0.1576961230479736</v>
+        <v>0.212206572769953</v>
       </c>
       <c r="K2">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="L2">
-        <v>0.1676855895196507</v>
+        <v>0.2112676056338028</v>
       </c>
       <c r="M2">
-        <v>6.96</v>
+        <v>1.96</v>
       </c>
       <c r="N2">
-        <v>0.2887966804979253</v>
+        <v>0.08099173553719008</v>
       </c>
       <c r="O2">
-        <v>1.8125</v>
+        <v>0.4355555555555555</v>
       </c>
       <c r="P2">
-        <v>6.96</v>
+        <v>1.96</v>
       </c>
       <c r="Q2">
-        <v>0.2887966804979253</v>
+        <v>0.08099173553719008</v>
       </c>
       <c r="R2">
-        <v>1.8125</v>
+        <v>0.4355555555555555</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,70 +635,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.16</v>
+        <v>6.74</v>
       </c>
       <c r="V2">
-        <v>0.2141078838174274</v>
+        <v>0.2785123966942149</v>
       </c>
       <c r="W2">
-        <v>0.2666666666666667</v>
+        <v>0.371900826446281</v>
       </c>
       <c r="X2">
-        <v>0.0670180324438194</v>
+        <v>0.1262860504693986</v>
       </c>
       <c r="Y2">
-        <v>0.1996486342228473</v>
+        <v>0.2456147759768824</v>
       </c>
       <c r="Z2">
-        <v>7.705248990578731</v>
+        <v>10.5759682224429</v>
       </c>
       <c r="AA2">
-        <v>1.215087892933578</v>
+        <v>2.24428997020854</v>
       </c>
       <c r="AB2">
-        <v>0.06616697562164879</v>
+        <v>0.1253000650775791</v>
       </c>
       <c r="AC2">
-        <v>1.148920917311929</v>
+        <v>2.118989905130961</v>
       </c>
       <c r="AD2">
-        <v>0.454</v>
+        <v>0.284</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.454</v>
+        <v>0.284</v>
       </c>
       <c r="AG2">
-        <v>-4.706</v>
+        <v>-6.456</v>
       </c>
       <c r="AH2">
-        <v>0.01848985908609595</v>
+        <v>0.01159941186080706</v>
       </c>
       <c r="AI2">
-        <v>0.03616377250278795</v>
+        <v>0.02106199940670424</v>
       </c>
       <c r="AJ2">
-        <v>-0.242652366711354</v>
+        <v>-0.3638412984670875</v>
       </c>
       <c r="AK2">
-        <v>-0.6364619962131459</v>
+        <v>-0.9572953736654807</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AM2">
-        <v>-0.05</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="AN2">
-        <v>0.1110024449877751</v>
+        <v>0.06055437100213219</v>
+      </c>
+      <c r="AO2">
+        <v>237.8947368421053</v>
       </c>
       <c r="AP2">
-        <v>-1.150611246943765</v>
+        <v>-1.376545842217484</v>
       </c>
       <c r="AQ2">
-        <v>-80</v>
+        <v>-4519.999999999995</v>
       </c>
     </row>
     <row r="3">
@@ -716,43 +721,43 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.159</v>
+        <v>-0.08839999999999999</v>
       </c>
       <c r="G3">
-        <v>0.1696069868995633</v>
+        <v>0.2206572769953052</v>
       </c>
       <c r="H3">
-        <v>0.1689956331877729</v>
+        <v>0.2206572769953052</v>
       </c>
       <c r="I3">
-        <v>0.1746724890829695</v>
+        <v>0.212206572769953</v>
       </c>
       <c r="J3">
-        <v>0.1576961230479736</v>
+        <v>0.212206572769953</v>
       </c>
       <c r="K3">
-        <v>3.84</v>
+        <v>4.5</v>
       </c>
       <c r="L3">
-        <v>0.1676855895196507</v>
+        <v>0.2112676056338028</v>
       </c>
       <c r="M3">
-        <v>6.96</v>
+        <v>1.96</v>
       </c>
       <c r="N3">
-        <v>0.2887966804979253</v>
+        <v>0.08099173553719008</v>
       </c>
       <c r="O3">
-        <v>1.8125</v>
+        <v>0.4355555555555555</v>
       </c>
       <c r="P3">
-        <v>6.96</v>
+        <v>1.96</v>
       </c>
       <c r="Q3">
-        <v>0.2887966804979253</v>
+        <v>0.08099173553719008</v>
       </c>
       <c r="R3">
-        <v>1.8125</v>
+        <v>0.4355555555555555</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -761,70 +766,8785 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.16</v>
+        <v>6.74</v>
       </c>
       <c r="V3">
-        <v>0.2141078838174274</v>
+        <v>0.2785123966942149</v>
       </c>
       <c r="W3">
-        <v>0.2666666666666667</v>
+        <v>0.371900826446281</v>
       </c>
       <c r="X3">
-        <v>0.0670180324438194</v>
+        <v>0.1262860504693986</v>
       </c>
       <c r="Y3">
-        <v>0.1996486342228473</v>
+        <v>0.2456147759768824</v>
       </c>
       <c r="Z3">
-        <v>7.705248990578731</v>
+        <v>10.5759682224429</v>
       </c>
       <c r="AA3">
-        <v>1.215087892933578</v>
+        <v>2.24428997020854</v>
       </c>
       <c r="AB3">
-        <v>0.06616697562164879</v>
+        <v>0.1253000650775791</v>
       </c>
       <c r="AC3">
-        <v>1.148920917311929</v>
+        <v>2.118989905130961</v>
       </c>
       <c r="AD3">
-        <v>0.454</v>
+        <v>0.284</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.454</v>
+        <v>0.284</v>
       </c>
       <c r="AG3">
-        <v>-4.706</v>
+        <v>-6.456</v>
       </c>
       <c r="AH3">
-        <v>0.01848985908609595</v>
+        <v>0.01159941186080706</v>
       </c>
       <c r="AI3">
-        <v>0.03616377250278795</v>
+        <v>0.02106199940670424</v>
       </c>
       <c r="AJ3">
-        <v>-0.242652366711354</v>
+        <v>-0.3638412984670875</v>
       </c>
       <c r="AK3">
-        <v>-0.6364619962131459</v>
+        <v>-0.9572953736654807</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.019</v>
       </c>
       <c r="AM3">
-        <v>-0.05</v>
+        <v>-0.001000000000000001</v>
       </c>
       <c r="AN3">
-        <v>0.1110024449877751</v>
+        <v>0.06055437100213219</v>
+      </c>
+      <c r="AO3">
+        <v>237.8947368421053</v>
       </c>
       <c r="AP3">
-        <v>-1.150611246943765</v>
+        <v>-1.376545842217484</v>
       </c>
       <c r="AQ3">
-        <v>-80</v>
+        <v>-4519.999999999995</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>DNXCorp SE (ENXTPA:ALDNX)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTPA:ALDNX</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Software (Entertainment)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0115994118608071</v>
+      </c>
+      <c r="F2">
+        <v>0.73</v>
+      </c>
+      <c r="G2">
+        <v>24.2</v>
+      </c>
+      <c r="H2">
+        <v>8.05119802900226</v>
+      </c>
+      <c r="I2">
+        <v>17.744</v>
+      </c>
+      <c r="J2">
+        <v>19.1845180290023</v>
+      </c>
+      <c r="K2">
+        <v>0.284</v>
+      </c>
+      <c r="L2">
+        <v>17.87332</v>
+      </c>
+      <c r="M2">
+        <v>0.125300065077579</v>
+      </c>
+      <c r="N2">
+        <v>0.111545925090386</v>
+      </c>
+      <c r="O2">
+        <v>0.041283</v>
+      </c>
+      <c r="P2">
+        <v>0.041283</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.126286050469399</v>
+      </c>
+      <c r="T2">
+        <v>0.30151605589032</v>
+      </c>
+      <c r="U2">
+        <v>1.47924409340939</v>
+      </c>
+      <c r="V2">
+        <v>4.44209301750912</v>
+      </c>
+      <c r="W2">
+        <v>4.519687343024026</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>24.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.0591424031092525</v>
+      </c>
+      <c r="AC2">
+        <v>0.055</v>
+      </c>
+      <c r="AD2">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>4.69</v>
+      </c>
+      <c r="AH2">
+        <v>0.247</v>
+      </c>
+      <c r="AI2">
+        <v>0.1319999999999997</v>
+      </c>
+      <c r="AJ2">
+        <v>0.284</v>
+      </c>
+      <c r="AK2">
+        <v>0.284</v>
+      </c>
+      <c r="AL2">
+        <v>0.019</v>
+      </c>
+      <c r="AM2">
+        <v>0.284</v>
+      </c>
+      <c r="AN2">
+        <v>6.74</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.125522141642015</v>
+      </c>
+      <c r="C2">
+        <v>24.46251366142094</v>
+      </c>
+      <c r="D2">
+        <v>17.72251366142094</v>
+      </c>
+      <c r="E2">
+        <v>-0.284</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>6.74</v>
+      </c>
+      <c r="H2">
+        <v>24.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>4.69</v>
+      </c>
+      <c r="K2">
+        <v>0.247</v>
+      </c>
+      <c r="L2">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="O2">
+        <v>1.108084200000001</v>
+      </c>
+      <c r="P2">
+        <v>3.3349158</v>
+      </c>
+      <c r="Q2">
+        <v>3.5819158</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.125522141642015</v>
+      </c>
+      <c r="T2">
+        <v>1.466327661421113</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W2">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1252608808207598</v>
+      </c>
+      <c r="C3">
+        <v>24.24295656134024</v>
+      </c>
+      <c r="D3">
+        <v>17.74779656134024</v>
+      </c>
+      <c r="E3">
+        <v>-0.03916</v>
+      </c>
+      <c r="F3">
+        <v>0.24484</v>
+      </c>
+      <c r="G3">
+        <v>6.74</v>
+      </c>
+      <c r="H3">
+        <v>24.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>4.69</v>
+      </c>
+      <c r="K3">
+        <v>0.247</v>
+      </c>
+      <c r="L3">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M3">
+        <v>0.011189188</v>
+      </c>
+      <c r="N3">
+        <v>4.431810812</v>
+      </c>
+      <c r="O3">
+        <v>1.105293616512801</v>
+      </c>
+      <c r="P3">
+        <v>3.326517195487199</v>
+      </c>
+      <c r="Q3">
+        <v>3.573517195487199</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1261796531522826</v>
+      </c>
+      <c r="T3">
+        <v>1.477445091144978</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W3">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>397.0797523466404</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1249996199995046</v>
+      </c>
+      <c r="C4">
+        <v>24.02347170137857</v>
+      </c>
+      <c r="D4">
+        <v>17.77315170137857</v>
+      </c>
+      <c r="E4">
+        <v>0.20568</v>
+      </c>
+      <c r="F4">
+        <v>0.4896799999999999</v>
+      </c>
+      <c r="G4">
+        <v>6.74</v>
+      </c>
+      <c r="H4">
+        <v>24.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>4.69</v>
+      </c>
+      <c r="K4">
+        <v>0.247</v>
+      </c>
+      <c r="L4">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M4">
+        <v>0.022378376</v>
+      </c>
+      <c r="N4">
+        <v>4.420621624000001</v>
+      </c>
+      <c r="O4">
+        <v>1.102503033025601</v>
+      </c>
+      <c r="P4">
+        <v>3.3181185909744</v>
+      </c>
+      <c r="Q4">
+        <v>3.5651185909744</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1268505832648006</v>
+      </c>
+      <c r="T4">
+        <v>1.488789407189739</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W4">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>198.5398761733202</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1247383591782494</v>
+      </c>
+      <c r="C5">
+        <v>23.80405939159337</v>
+      </c>
+      <c r="D5">
+        <v>17.79857939159337</v>
+      </c>
+      <c r="E5">
+        <v>0.45052</v>
+      </c>
+      <c r="F5">
+        <v>0.73452</v>
+      </c>
+      <c r="G5">
+        <v>6.74</v>
+      </c>
+      <c r="H5">
+        <v>24.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>4.69</v>
+      </c>
+      <c r="K5">
+        <v>0.247</v>
+      </c>
+      <c r="L5">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M5">
+        <v>0.033567564</v>
+      </c>
+      <c r="N5">
+        <v>4.409432436</v>
+      </c>
+      <c r="O5">
+        <v>1.099712449538401</v>
+      </c>
+      <c r="P5">
+        <v>3.309719986461599</v>
+      </c>
+      <c r="Q5">
+        <v>3.556719986461599</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.127535346987886</v>
+      </c>
+      <c r="T5">
+        <v>1.500367626658103</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W5">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>132.3599174488801</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1244770983569942</v>
+      </c>
+      <c r="C6">
+        <v>23.58471994381902</v>
+      </c>
+      <c r="D6">
+        <v>17.82407994381902</v>
+      </c>
+      <c r="E6">
+        <v>0.69536</v>
+      </c>
+      <c r="F6">
+        <v>0.9793599999999999</v>
+      </c>
+      <c r="G6">
+        <v>6.74</v>
+      </c>
+      <c r="H6">
+        <v>24.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>4.69</v>
+      </c>
+      <c r="K6">
+        <v>0.247</v>
+      </c>
+      <c r="L6">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M6">
+        <v>0.044756752</v>
+      </c>
+      <c r="N6">
+        <v>4.398243248000001</v>
+      </c>
+      <c r="O6">
+        <v>1.096921866051201</v>
+      </c>
+      <c r="P6">
+        <v>3.3013213819488</v>
+      </c>
+      <c r="Q6">
+        <v>3.5483213819488</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.128234376621869</v>
+      </c>
+      <c r="T6">
+        <v>1.512187059032058</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W6">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>99.26993808666012</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.124215837535739</v>
+      </c>
+      <c r="C7">
+        <v>23.36545367167953</v>
+      </c>
+      <c r="D7">
+        <v>17.84965367167953</v>
+      </c>
+      <c r="E7">
+        <v>0.9401999999999999</v>
+      </c>
+      <c r="F7">
+        <v>1.2242</v>
+      </c>
+      <c r="G7">
+        <v>6.74</v>
+      </c>
+      <c r="H7">
+        <v>24.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>4.69</v>
+      </c>
+      <c r="K7">
+        <v>0.247</v>
+      </c>
+      <c r="L7">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M7">
+        <v>0.05594594000000001</v>
+      </c>
+      <c r="N7">
+        <v>4.387054060000001</v>
+      </c>
+      <c r="O7">
+        <v>1.094131282564001</v>
+      </c>
+      <c r="P7">
+        <v>3.292922777436</v>
+      </c>
+      <c r="Q7">
+        <v>3.539922777436</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.128948122669199</v>
+      </c>
+      <c r="T7">
+        <v>1.524255321561254</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W7">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>79.41595046932807</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1239545767144839</v>
+      </c>
+      <c r="C8">
+        <v>23.14626089060145</v>
+      </c>
+      <c r="D8">
+        <v>17.87530089060145</v>
+      </c>
+      <c r="E8">
+        <v>1.18504</v>
+      </c>
+      <c r="F8">
+        <v>1.46904</v>
+      </c>
+      <c r="G8">
+        <v>6.74</v>
+      </c>
+      <c r="H8">
+        <v>24.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>4.69</v>
+      </c>
+      <c r="K8">
+        <v>0.247</v>
+      </c>
+      <c r="L8">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M8">
+        <v>0.067135128</v>
+      </c>
+      <c r="N8">
+        <v>4.375864872</v>
+      </c>
+      <c r="O8">
+        <v>1.091340699076801</v>
+      </c>
+      <c r="P8">
+        <v>3.2845241729232</v>
+      </c>
+      <c r="Q8">
+        <v>3.531524172923199</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1296770548026424</v>
+      </c>
+      <c r="T8">
+        <v>1.536580355633625</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W8">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>66.17995872444006</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1236933158932287</v>
+      </c>
+      <c r="C9">
+        <v>22.92714191782682</v>
+      </c>
+      <c r="D9">
+        <v>17.90102191782682</v>
+      </c>
+      <c r="E9">
+        <v>1.42988</v>
+      </c>
+      <c r="F9">
+        <v>1.71388</v>
+      </c>
+      <c r="G9">
+        <v>6.74</v>
+      </c>
+      <c r="H9">
+        <v>24.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>4.69</v>
+      </c>
+      <c r="K9">
+        <v>0.247</v>
+      </c>
+      <c r="L9">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M9">
+        <v>0.078324316</v>
+      </c>
+      <c r="N9">
+        <v>4.364675684000001</v>
+      </c>
+      <c r="O9">
+        <v>1.088550115589601</v>
+      </c>
+      <c r="P9">
+        <v>3.2761255684104</v>
+      </c>
+      <c r="Q9">
+        <v>3.5231255684104</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1304216628959448</v>
+      </c>
+      <c r="T9">
+        <v>1.549170444202176</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W9">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>56.72567890666291</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1234320550719735</v>
+      </c>
+      <c r="C10">
+        <v>22.70809707242623</v>
+      </c>
+      <c r="D10">
+        <v>17.92681707242623</v>
+      </c>
+      <c r="E10">
+        <v>1.67472</v>
+      </c>
+      <c r="F10">
+        <v>1.95872</v>
+      </c>
+      <c r="G10">
+        <v>6.74</v>
+      </c>
+      <c r="H10">
+        <v>24.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>4.69</v>
+      </c>
+      <c r="K10">
+        <v>0.247</v>
+      </c>
+      <c r="L10">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M10">
+        <v>0.08951350399999999</v>
+      </c>
+      <c r="N10">
+        <v>4.353486496</v>
+      </c>
+      <c r="O10">
+        <v>1.085759532102401</v>
+      </c>
+      <c r="P10">
+        <v>3.2677269638976</v>
+      </c>
+      <c r="Q10">
+        <v>3.5147269638976</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1311824581217103</v>
+      </c>
+      <c r="T10">
+        <v>1.562034230348303</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W10">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>49.63496904333005</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1231707942507183</v>
+      </c>
+      <c r="C11">
+        <v>22.48912667531205</v>
+      </c>
+      <c r="D11">
+        <v>17.95268667531205</v>
+      </c>
+      <c r="E11">
+        <v>1.91956</v>
+      </c>
+      <c r="F11">
+        <v>2.20356</v>
+      </c>
+      <c r="G11">
+        <v>6.74</v>
+      </c>
+      <c r="H11">
+        <v>24.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>4.69</v>
+      </c>
+      <c r="K11">
+        <v>0.247</v>
+      </c>
+      <c r="L11">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M11">
+        <v>0.100702692</v>
+      </c>
+      <c r="N11">
+        <v>4.342297308000001</v>
+      </c>
+      <c r="O11">
+        <v>1.082968948615201</v>
+      </c>
+      <c r="P11">
+        <v>3.2593283593848</v>
+      </c>
+      <c r="Q11">
+        <v>3.5063283593848</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1319599741216685</v>
+      </c>
+      <c r="T11">
+        <v>1.575180737069071</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W11">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>44.11997248296004</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1229095334294631</v>
+      </c>
+      <c r="C12">
+        <v>22.27023104925171</v>
+      </c>
+      <c r="D12">
+        <v>17.9786310492517</v>
+      </c>
+      <c r="E12">
+        <v>2.1644</v>
+      </c>
+      <c r="F12">
+        <v>2.4484</v>
+      </c>
+      <c r="G12">
+        <v>6.74</v>
+      </c>
+      <c r="H12">
+        <v>24.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>4.69</v>
+      </c>
+      <c r="K12">
+        <v>0.247</v>
+      </c>
+      <c r="L12">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M12">
+        <v>0.11189188</v>
+      </c>
+      <c r="N12">
+        <v>4.331108120000001</v>
+      </c>
+      <c r="O12">
+        <v>1.080178365128001</v>
+      </c>
+      <c r="P12">
+        <v>3.250929754872</v>
+      </c>
+      <c r="Q12">
+        <v>3.497929754872</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.132754768254959</v>
+      </c>
+      <c r="T12">
+        <v>1.588619388383634</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W12">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>39.70797523466403</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1226482726082079</v>
+      </c>
+      <c r="C13">
+        <v>22.05141051888111</v>
+      </c>
+      <c r="D13">
+        <v>18.00465051888111</v>
+      </c>
+      <c r="E13">
+        <v>2.40924</v>
+      </c>
+      <c r="F13">
+        <v>2.69324</v>
+      </c>
+      <c r="G13">
+        <v>6.74</v>
+      </c>
+      <c r="H13">
+        <v>24.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>4.69</v>
+      </c>
+      <c r="K13">
+        <v>0.247</v>
+      </c>
+      <c r="L13">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M13">
+        <v>0.123081068</v>
+      </c>
+      <c r="N13">
+        <v>4.319918932</v>
+      </c>
+      <c r="O13">
+        <v>1.077387781640801</v>
+      </c>
+      <c r="P13">
+        <v>3.242531150359199</v>
+      </c>
+      <c r="Q13">
+        <v>3.489531150359199</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1335674229305707</v>
+      </c>
+      <c r="T13">
+        <v>1.602360031862569</v>
+      </c>
+      <c r="U13">
+        <v>0.0457</v>
+      </c>
+      <c r="V13">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W13">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>36.09815930424003</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1223870117869527</v>
+      </c>
+      <c r="C14">
+        <v>21.83266541071824</v>
+      </c>
+      <c r="D14">
+        <v>18.03074541071824</v>
+      </c>
+      <c r="E14">
+        <v>2.65408</v>
+      </c>
+      <c r="F14">
+        <v>2.93808</v>
+      </c>
+      <c r="G14">
+        <v>6.74</v>
+      </c>
+      <c r="H14">
+        <v>24.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>4.69</v>
+      </c>
+      <c r="K14">
+        <v>0.247</v>
+      </c>
+      <c r="L14">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M14">
+        <v>0.134270256</v>
+      </c>
+      <c r="N14">
+        <v>4.308729744000001</v>
+      </c>
+      <c r="O14">
+        <v>1.074597198153601</v>
+      </c>
+      <c r="P14">
+        <v>3.2341325458464</v>
+      </c>
+      <c r="Q14">
+        <v>3.4811325458464</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1343985470306281</v>
+      </c>
+      <c r="T14">
+        <v>1.616412962693297</v>
+      </c>
+      <c r="U14">
+        <v>0.0457</v>
+      </c>
+      <c r="V14">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W14">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>33.08997936222003</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1221257509656976</v>
+      </c>
+      <c r="C15">
+        <v>21.61399605317673</v>
+      </c>
+      <c r="D15">
+        <v>18.05691605317673</v>
+      </c>
+      <c r="E15">
+        <v>2.89892</v>
+      </c>
+      <c r="F15">
+        <v>3.18292</v>
+      </c>
+      <c r="G15">
+        <v>6.74</v>
+      </c>
+      <c r="H15">
+        <v>24.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>4.69</v>
+      </c>
+      <c r="K15">
+        <v>0.247</v>
+      </c>
+      <c r="L15">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M15">
+        <v>0.145459444</v>
+      </c>
+      <c r="N15">
+        <v>4.297540556</v>
+      </c>
+      <c r="O15">
+        <v>1.071806614666401</v>
+      </c>
+      <c r="P15">
+        <v>3.225733941333599</v>
+      </c>
+      <c r="Q15">
+        <v>3.472733941333599</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1352487774318363</v>
+      </c>
+      <c r="T15">
+        <v>1.630788949405193</v>
+      </c>
+      <c r="U15">
+        <v>0.0457</v>
+      </c>
+      <c r="V15">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W15">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>30.54459633435695</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1218644901444424</v>
+      </c>
+      <c r="C16">
+        <v>21.3954027765797</v>
+      </c>
+      <c r="D16">
+        <v>18.0831627765797</v>
+      </c>
+      <c r="E16">
+        <v>3.14376</v>
+      </c>
+      <c r="F16">
+        <v>3.42776</v>
+      </c>
+      <c r="G16">
+        <v>6.74</v>
+      </c>
+      <c r="H16">
+        <v>24.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>4.69</v>
+      </c>
+      <c r="K16">
+        <v>0.247</v>
+      </c>
+      <c r="L16">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M16">
+        <v>0.156648632</v>
+      </c>
+      <c r="N16">
+        <v>4.286351368</v>
+      </c>
+      <c r="O16">
+        <v>1.069016031179201</v>
+      </c>
+      <c r="P16">
+        <v>3.217335336820799</v>
+      </c>
+      <c r="Q16">
+        <v>3.464335336820799</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1361187806330725</v>
+      </c>
+      <c r="T16">
+        <v>1.645499261389457</v>
+      </c>
+      <c r="U16">
+        <v>0.0457</v>
+      </c>
+      <c r="V16">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W16">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>28.36283945333145</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1216032293231872</v>
+      </c>
+      <c r="C17">
+        <v>21.17688591317365</v>
+      </c>
+      <c r="D17">
+        <v>18.10948591317365</v>
+      </c>
+      <c r="E17">
+        <v>3.3886</v>
+      </c>
+      <c r="F17">
+        <v>3.6726</v>
+      </c>
+      <c r="G17">
+        <v>6.74</v>
+      </c>
+      <c r="H17">
+        <v>24.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>4.69</v>
+      </c>
+      <c r="K17">
+        <v>0.247</v>
+      </c>
+      <c r="L17">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M17">
+        <v>0.16783782</v>
+      </c>
+      <c r="N17">
+        <v>4.275162180000001</v>
+      </c>
+      <c r="O17">
+        <v>1.066225447692001</v>
+      </c>
+      <c r="P17">
+        <v>3.208936732308</v>
+      </c>
+      <c r="Q17">
+        <v>3.455936732307999</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1370092544978673</v>
+      </c>
+      <c r="T17">
+        <v>1.660555698361587</v>
+      </c>
+      <c r="U17">
+        <v>0.0457</v>
+      </c>
+      <c r="V17">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W17">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>26.47198348977603</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.121341968501932</v>
+      </c>
+      <c r="C18">
+        <v>20.95844579714242</v>
+      </c>
+      <c r="D18">
+        <v>18.13588579714242</v>
+      </c>
+      <c r="E18">
+        <v>3.63344</v>
+      </c>
+      <c r="F18">
+        <v>3.91744</v>
+      </c>
+      <c r="G18">
+        <v>6.74</v>
+      </c>
+      <c r="H18">
+        <v>24.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>4.69</v>
+      </c>
+      <c r="K18">
+        <v>0.247</v>
+      </c>
+      <c r="L18">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M18">
+        <v>0.179027008</v>
+      </c>
+      <c r="N18">
+        <v>4.263972992</v>
+      </c>
+      <c r="O18">
+        <v>1.063434864204801</v>
+      </c>
+      <c r="P18">
+        <v>3.200538127795199</v>
+      </c>
+      <c r="Q18">
+        <v>3.447538127795199</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1379209301213477</v>
+      </c>
+      <c r="T18">
+        <v>1.675970621928291</v>
+      </c>
+      <c r="U18">
+        <v>0.0457</v>
+      </c>
+      <c r="V18">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W18">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>24.81748452166503</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1210807076806768</v>
+      </c>
+      <c r="C19">
+        <v>20.74008276462145</v>
+      </c>
+      <c r="D19">
+        <v>18.16236276462145</v>
+      </c>
+      <c r="E19">
+        <v>3.87828</v>
+      </c>
+      <c r="F19">
+        <v>4.16228</v>
+      </c>
+      <c r="G19">
+        <v>6.74</v>
+      </c>
+      <c r="H19">
+        <v>24.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>4.69</v>
+      </c>
+      <c r="K19">
+        <v>0.247</v>
+      </c>
+      <c r="L19">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M19">
+        <v>0.190216196</v>
+      </c>
+      <c r="N19">
+        <v>4.252783804000001</v>
+      </c>
+      <c r="O19">
+        <v>1.060644280717601</v>
+      </c>
+      <c r="P19">
+        <v>3.1921395232824</v>
+      </c>
+      <c r="Q19">
+        <v>3.4391395232824</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1388545738321408</v>
+      </c>
+      <c r="T19">
+        <v>1.691756989436362</v>
+      </c>
+      <c r="U19">
+        <v>0.0457</v>
+      </c>
+      <c r="V19">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W19">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>23.35763249097885</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1208194468594216</v>
+      </c>
+      <c r="C20">
+        <v>20.52179715371191</v>
+      </c>
+      <c r="D20">
+        <v>18.18891715371191</v>
+      </c>
+      <c r="E20">
+        <v>4.12312</v>
+      </c>
+      <c r="F20">
+        <v>4.40712</v>
+      </c>
+      <c r="G20">
+        <v>6.74</v>
+      </c>
+      <c r="H20">
+        <v>24.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>4.69</v>
+      </c>
+      <c r="K20">
+        <v>0.247</v>
+      </c>
+      <c r="L20">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M20">
+        <v>0.201405384</v>
+      </c>
+      <c r="N20">
+        <v>4.241594616</v>
+      </c>
+      <c r="O20">
+        <v>1.057853697230401</v>
+      </c>
+      <c r="P20">
+        <v>3.183740918769599</v>
+      </c>
+      <c r="Q20">
+        <v>3.430740918769599</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1398109893407581</v>
+      </c>
+      <c r="T20">
+        <v>1.707928390298288</v>
+      </c>
+      <c r="U20">
+        <v>0.0457</v>
+      </c>
+      <c r="V20">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W20">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>22.05998624148002</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1205581860381665</v>
+      </c>
+      <c r="C21">
+        <v>20.30358930449519</v>
+      </c>
+      <c r="D21">
+        <v>18.21554930449519</v>
+      </c>
+      <c r="E21">
+        <v>4.36796</v>
+      </c>
+      <c r="F21">
+        <v>4.65196</v>
+      </c>
+      <c r="G21">
+        <v>6.74</v>
+      </c>
+      <c r="H21">
+        <v>24.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>4.69</v>
+      </c>
+      <c r="K21">
+        <v>0.247</v>
+      </c>
+      <c r="L21">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M21">
+        <v>0.212594572</v>
+      </c>
+      <c r="N21">
+        <v>4.230405428</v>
+      </c>
+      <c r="O21">
+        <v>1.055063113743201</v>
+      </c>
+      <c r="P21">
+        <v>3.175342314256799</v>
+      </c>
+      <c r="Q21">
+        <v>3.422342314256799</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1407910200471191</v>
+      </c>
+      <c r="T21">
+        <v>1.724499085008657</v>
+      </c>
+      <c r="U21">
+        <v>0.0457</v>
+      </c>
+      <c r="V21">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W21">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>20.8989343340337</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1202969252169113</v>
+      </c>
+      <c r="C22">
+        <v>20.08545955904738</v>
+      </c>
+      <c r="D22">
+        <v>18.24225955904738</v>
+      </c>
+      <c r="E22">
+        <v>4.6128</v>
+      </c>
+      <c r="F22">
+        <v>4.8968</v>
+      </c>
+      <c r="G22">
+        <v>6.74</v>
+      </c>
+      <c r="H22">
+        <v>24.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>4.69</v>
+      </c>
+      <c r="K22">
+        <v>0.247</v>
+      </c>
+      <c r="L22">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M22">
+        <v>0.22378376</v>
+      </c>
+      <c r="N22">
+        <v>4.219216240000001</v>
+      </c>
+      <c r="O22">
+        <v>1.052272530256001</v>
+      </c>
+      <c r="P22">
+        <v>3.166943709743999</v>
+      </c>
+      <c r="Q22">
+        <v>3.413943709743999</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1417955515211391</v>
+      </c>
+      <c r="T22">
+        <v>1.741484047086785</v>
+      </c>
+      <c r="U22">
+        <v>0.0457</v>
+      </c>
+      <c r="V22">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W22">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>19.85398761733202</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1200356643956561</v>
+      </c>
+      <c r="C23">
+        <v>19.86740826145391</v>
+      </c>
+      <c r="D23">
+        <v>18.26904826145391</v>
+      </c>
+      <c r="E23">
+        <v>4.85764</v>
+      </c>
+      <c r="F23">
+        <v>5.14164</v>
+      </c>
+      <c r="G23">
+        <v>6.74</v>
+      </c>
+      <c r="H23">
+        <v>24.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>4.69</v>
+      </c>
+      <c r="K23">
+        <v>0.247</v>
+      </c>
+      <c r="L23">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M23">
+        <v>0.234972948</v>
+      </c>
+      <c r="N23">
+        <v>4.208027052</v>
+      </c>
+      <c r="O23">
+        <v>1.049481946768801</v>
+      </c>
+      <c r="P23">
+        <v>3.158545105231199</v>
+      </c>
+      <c r="Q23">
+        <v>3.405545105231199</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1428255141717165</v>
+      </c>
+      <c r="T23">
+        <v>1.758899008204865</v>
+      </c>
+      <c r="U23">
+        <v>0.0457</v>
+      </c>
+      <c r="V23">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W23">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>18.9085596355543</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1197744035744009</v>
+      </c>
+      <c r="C24">
+        <v>19.64943575782436</v>
+      </c>
+      <c r="D24">
+        <v>18.29591575782435</v>
+      </c>
+      <c r="E24">
+        <v>5.10248</v>
+      </c>
+      <c r="F24">
+        <v>5.38648</v>
+      </c>
+      <c r="G24">
+        <v>6.74</v>
+      </c>
+      <c r="H24">
+        <v>24.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>4.69</v>
+      </c>
+      <c r="K24">
+        <v>0.247</v>
+      </c>
+      <c r="L24">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M24">
+        <v>0.246162136</v>
+      </c>
+      <c r="N24">
+        <v>4.196837864000001</v>
+      </c>
+      <c r="O24">
+        <v>1.046691363281601</v>
+      </c>
+      <c r="P24">
+        <v>3.1501465007184</v>
+      </c>
+      <c r="Q24">
+        <v>3.3971465007184</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1438818861210268</v>
+      </c>
+      <c r="T24">
+        <v>1.776760506787512</v>
+      </c>
+      <c r="U24">
+        <v>0.0457</v>
+      </c>
+      <c r="V24">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W24">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>18.04907965212002</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1195131427531457</v>
+      </c>
+      <c r="C25">
+        <v>19.4315423963073</v>
+      </c>
+      <c r="D25">
+        <v>18.32286239630729</v>
+      </c>
+      <c r="E25">
+        <v>5.34732</v>
+      </c>
+      <c r="F25">
+        <v>5.63132</v>
+      </c>
+      <c r="G25">
+        <v>6.74</v>
+      </c>
+      <c r="H25">
+        <v>24.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>4.69</v>
+      </c>
+      <c r="K25">
+        <v>0.247</v>
+      </c>
+      <c r="L25">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M25">
+        <v>0.257351324</v>
+      </c>
+      <c r="N25">
+        <v>4.185648676</v>
+      </c>
+      <c r="O25">
+        <v>1.043900779794401</v>
+      </c>
+      <c r="P25">
+        <v>3.1417478962056</v>
+      </c>
+      <c r="Q25">
+        <v>3.388747896205599</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1449656963027866</v>
+      </c>
+      <c r="T25">
+        <v>1.795085940398279</v>
+      </c>
+      <c r="U25">
+        <v>0.0457</v>
+      </c>
+      <c r="V25">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W25">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>17.26433705854958</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1192518819318905</v>
+      </c>
+      <c r="C26">
+        <v>19.21372852710542</v>
+      </c>
+      <c r="D26">
+        <v>18.34988852710541</v>
+      </c>
+      <c r="E26">
+        <v>5.59216</v>
+      </c>
+      <c r="F26">
+        <v>5.87616</v>
+      </c>
+      <c r="G26">
+        <v>6.74</v>
+      </c>
+      <c r="H26">
+        <v>24.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>4.69</v>
+      </c>
+      <c r="K26">
+        <v>0.247</v>
+      </c>
+      <c r="L26">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M26">
+        <v>0.268540512</v>
+      </c>
+      <c r="N26">
+        <v>4.174459488</v>
+      </c>
+      <c r="O26">
+        <v>1.041110196307201</v>
+      </c>
+      <c r="P26">
+        <v>3.1333492916928</v>
+      </c>
+      <c r="Q26">
+        <v>3.3803492916928</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1460780278051191</v>
+      </c>
+      <c r="T26">
+        <v>1.813893622261961</v>
+      </c>
+      <c r="U26">
+        <v>0.0457</v>
+      </c>
+      <c r="V26">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W26">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>16.54498968111001</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1189906211106353</v>
+      </c>
+      <c r="C27">
+        <v>18.9959945024906</v>
+      </c>
+      <c r="D27">
+        <v>18.3769945024906</v>
+      </c>
+      <c r="E27">
+        <v>5.837</v>
+      </c>
+      <c r="F27">
+        <v>6.121</v>
+      </c>
+      <c r="G27">
+        <v>6.74</v>
+      </c>
+      <c r="H27">
+        <v>24.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>4.69</v>
+      </c>
+      <c r="K27">
+        <v>0.247</v>
+      </c>
+      <c r="L27">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M27">
+        <v>0.2797297</v>
+      </c>
+      <c r="N27">
+        <v>4.163270300000001</v>
+      </c>
+      <c r="O27">
+        <v>1.038319612820001</v>
+      </c>
+      <c r="P27">
+        <v>3.12495068718</v>
+      </c>
+      <c r="Q27">
+        <v>3.37195068718</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1472200214808471</v>
+      </c>
+      <c r="T27">
+        <v>1.833202842308675</v>
+      </c>
+      <c r="U27">
+        <v>0.0457</v>
+      </c>
+      <c r="V27">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W27">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>15.88319009386561</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1187293602893802</v>
+      </c>
+      <c r="C28">
+        <v>18.77834067681932</v>
+      </c>
+      <c r="D28">
+        <v>18.40418067681932</v>
+      </c>
+      <c r="E28">
+        <v>6.08184</v>
+      </c>
+      <c r="F28">
+        <v>6.365839999999999</v>
+      </c>
+      <c r="G28">
+        <v>6.74</v>
+      </c>
+      <c r="H28">
+        <v>24.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>4.69</v>
+      </c>
+      <c r="K28">
+        <v>0.247</v>
+      </c>
+      <c r="L28">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M28">
+        <v>0.290918888</v>
+      </c>
+      <c r="N28">
+        <v>4.152081112</v>
+      </c>
+      <c r="O28">
+        <v>1.035529029332801</v>
+      </c>
+      <c r="P28">
+        <v>3.1165520826672</v>
+      </c>
+      <c r="Q28">
+        <v>3.3635520826672</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1483928798505137</v>
+      </c>
+      <c r="T28">
+        <v>1.853033933167463</v>
+      </c>
+      <c r="U28">
+        <v>0.0457</v>
+      </c>
+      <c r="V28">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W28">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>15.27229816717848</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.118468099468125</v>
+      </c>
+      <c r="C29">
+        <v>18.56076740654801</v>
+      </c>
+      <c r="D29">
+        <v>18.43144740654801</v>
+      </c>
+      <c r="E29">
+        <v>6.326680000000001</v>
+      </c>
+      <c r="F29">
+        <v>6.61068</v>
+      </c>
+      <c r="G29">
+        <v>6.74</v>
+      </c>
+      <c r="H29">
+        <v>24.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>4.69</v>
+      </c>
+      <c r="K29">
+        <v>0.247</v>
+      </c>
+      <c r="L29">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M29">
+        <v>0.3021080760000001</v>
+      </c>
+      <c r="N29">
+        <v>4.140891924000001</v>
+      </c>
+      <c r="O29">
+        <v>1.032738445845601</v>
+      </c>
+      <c r="P29">
+        <v>3.1081534781544</v>
+      </c>
+      <c r="Q29">
+        <v>3.3551534781544</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1495978713261986</v>
+      </c>
+      <c r="T29">
+        <v>1.873408341584025</v>
+      </c>
+      <c r="U29">
+        <v>0.0457</v>
+      </c>
+      <c r="V29">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W29">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>14.70665749432001</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1182068386468698</v>
+      </c>
+      <c r="C30">
+        <v>18.34327505024868</v>
+      </c>
+      <c r="D30">
+        <v>18.45879505024868</v>
+      </c>
+      <c r="E30">
+        <v>6.57152</v>
+      </c>
+      <c r="F30">
+        <v>6.85552</v>
+      </c>
+      <c r="G30">
+        <v>6.74</v>
+      </c>
+      <c r="H30">
+        <v>24.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>4.69</v>
+      </c>
+      <c r="K30">
+        <v>0.247</v>
+      </c>
+      <c r="L30">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M30">
+        <v>0.313297264</v>
+      </c>
+      <c r="N30">
+        <v>4.129702736</v>
+      </c>
+      <c r="O30">
+        <v>1.029947862358401</v>
+      </c>
+      <c r="P30">
+        <v>3.0997548736416</v>
+      </c>
+      <c r="Q30">
+        <v>3.3467548736416</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1508363347873192</v>
+      </c>
+      <c r="T30">
+        <v>1.894348705789936</v>
+      </c>
+      <c r="U30">
+        <v>0.0457</v>
+      </c>
+      <c r="V30">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W30">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>14.18141972666573</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1179455778256146</v>
+      </c>
+      <c r="C31">
+        <v>18.12586396862463</v>
+      </c>
+      <c r="D31">
+        <v>18.48622396862463</v>
+      </c>
+      <c r="E31">
+        <v>6.81636</v>
+      </c>
+      <c r="F31">
+        <v>7.100359999999999</v>
+      </c>
+      <c r="G31">
+        <v>6.74</v>
+      </c>
+      <c r="H31">
+        <v>24.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>4.69</v>
+      </c>
+      <c r="K31">
+        <v>0.247</v>
+      </c>
+      <c r="L31">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M31">
+        <v>0.324486452</v>
+      </c>
+      <c r="N31">
+        <v>4.118513548</v>
+      </c>
+      <c r="O31">
+        <v>1.027157278871201</v>
+      </c>
+      <c r="P31">
+        <v>3.091356269128799</v>
+      </c>
+      <c r="Q31">
+        <v>3.338356269128799</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1521096845431191</v>
+      </c>
+      <c r="T31">
+        <v>1.915878939410098</v>
+      </c>
+      <c r="U31">
+        <v>0.0457</v>
+      </c>
+      <c r="V31">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W31">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>13.69240525333243</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1176843170043594</v>
+      </c>
+      <c r="C32">
+        <v>17.90853452452629</v>
+      </c>
+      <c r="D32">
+        <v>18.51373452452629</v>
+      </c>
+      <c r="E32">
+        <v>7.061199999999999</v>
+      </c>
+      <c r="F32">
+        <v>7.345199999999999</v>
+      </c>
+      <c r="G32">
+        <v>6.74</v>
+      </c>
+      <c r="H32">
+        <v>24.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>4.69</v>
+      </c>
+      <c r="K32">
+        <v>0.247</v>
+      </c>
+      <c r="L32">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M32">
+        <v>0.33567564</v>
+      </c>
+      <c r="N32">
+        <v>4.107324360000001</v>
+      </c>
+      <c r="O32">
+        <v>1.024366695384001</v>
+      </c>
+      <c r="P32">
+        <v>3.082957664616</v>
+      </c>
+      <c r="Q32">
+        <v>3.329957664616</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1534194157205134</v>
+      </c>
+      <c r="T32">
+        <v>1.938024322562264</v>
+      </c>
+      <c r="U32">
+        <v>0.0457</v>
+      </c>
+      <c r="V32">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W32">
+        <v>0.03430241999999999</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>13.23599174488801</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1177953537831042</v>
+      </c>
+      <c r="C33">
+        <v>17.65199244189784</v>
+      </c>
+      <c r="D33">
+        <v>18.50203244189783</v>
+      </c>
+      <c r="E33">
+        <v>7.306039999999999</v>
+      </c>
+      <c r="F33">
+        <v>7.590039999999999</v>
+      </c>
+      <c r="G33">
+        <v>6.74</v>
+      </c>
+      <c r="H33">
+        <v>24.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>4.69</v>
+      </c>
+      <c r="K33">
+        <v>0.247</v>
+      </c>
+      <c r="L33">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M33">
+        <v>0.359008892</v>
+      </c>
+      <c r="N33">
+        <v>4.083991108</v>
+      </c>
+      <c r="O33">
+        <v>1.018547382335201</v>
+      </c>
+      <c r="P33">
+        <v>3.0654437256648</v>
+      </c>
+      <c r="Q33">
+        <v>3.312443725664799</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1547671101204409</v>
+      </c>
+      <c r="T33">
+        <v>1.960811600878262</v>
+      </c>
+      <c r="U33">
+        <v>0.0473</v>
+      </c>
+      <c r="V33">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W33">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>12.37573803603728</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.117546102561849</v>
+      </c>
+      <c r="C34">
+        <v>17.43344153763591</v>
+      </c>
+      <c r="D34">
+        <v>18.52832153763591</v>
+      </c>
+      <c r="E34">
+        <v>7.550879999999999</v>
+      </c>
+      <c r="F34">
+        <v>7.834879999999999</v>
+      </c>
+      <c r="G34">
+        <v>6.74</v>
+      </c>
+      <c r="H34">
+        <v>24.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>4.69</v>
+      </c>
+      <c r="K34">
+        <v>0.247</v>
+      </c>
+      <c r="L34">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M34">
+        <v>0.370589824</v>
+      </c>
+      <c r="N34">
+        <v>4.072410176000001</v>
+      </c>
+      <c r="O34">
+        <v>1.015659097894401</v>
+      </c>
+      <c r="P34">
+        <v>3.0567510781056</v>
+      </c>
+      <c r="Q34">
+        <v>3.3037510781056</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1561544425909545</v>
+      </c>
+      <c r="T34">
+        <v>1.984269093262378</v>
+      </c>
+      <c r="U34">
+        <v>0.0473</v>
+      </c>
+      <c r="V34">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W34">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>11.98899622241112</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1172968513405938</v>
+      </c>
+      <c r="C35">
+        <v>17.21496544677033</v>
+      </c>
+      <c r="D35">
+        <v>18.55468544677033</v>
+      </c>
+      <c r="E35">
+        <v>7.79572</v>
+      </c>
+      <c r="F35">
+        <v>8.07972</v>
+      </c>
+      <c r="G35">
+        <v>6.74</v>
+      </c>
+      <c r="H35">
+        <v>24.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>4.69</v>
+      </c>
+      <c r="K35">
+        <v>0.247</v>
+      </c>
+      <c r="L35">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M35">
+        <v>0.382170756</v>
+      </c>
+      <c r="N35">
+        <v>4.060829244000001</v>
+      </c>
+      <c r="O35">
+        <v>1.012770813453601</v>
+      </c>
+      <c r="P35">
+        <v>3.0480584305464</v>
+      </c>
+      <c r="Q35">
+        <v>3.295058430546399</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1575831879710356</v>
+      </c>
+      <c r="T35">
+        <v>2.00842680929975</v>
+      </c>
+      <c r="U35">
+        <v>0.0473</v>
+      </c>
+      <c r="V35">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W35">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>11.62569330658048</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1170476001193387</v>
+      </c>
+      <c r="C36">
+        <v>16.99656448911159</v>
+      </c>
+      <c r="D36">
+        <v>18.58112448911159</v>
+      </c>
+      <c r="E36">
+        <v>8.040559999999999</v>
+      </c>
+      <c r="F36">
+        <v>8.32456</v>
+      </c>
+      <c r="G36">
+        <v>6.74</v>
+      </c>
+      <c r="H36">
+        <v>24.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>4.69</v>
+      </c>
+      <c r="K36">
+        <v>0.247</v>
+      </c>
+      <c r="L36">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M36">
+        <v>0.393751688</v>
+      </c>
+      <c r="N36">
+        <v>4.049248312</v>
+      </c>
+      <c r="O36">
+        <v>1.009882529012801</v>
+      </c>
+      <c r="P36">
+        <v>3.0393657829872</v>
+      </c>
+      <c r="Q36">
+        <v>3.2863657829872</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1590552286656647</v>
+      </c>
+      <c r="T36">
+        <v>2.033316577338255</v>
+      </c>
+      <c r="U36">
+        <v>0.0473</v>
+      </c>
+      <c r="V36">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W36">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>11.28376115050458</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1167983488980835</v>
+      </c>
+      <c r="C37">
+        <v>16.77823898629566</v>
+      </c>
+      <c r="D37">
+        <v>18.60763898629567</v>
+      </c>
+      <c r="E37">
+        <v>8.285399999999999</v>
+      </c>
+      <c r="F37">
+        <v>8.5694</v>
+      </c>
+      <c r="G37">
+        <v>6.74</v>
+      </c>
+      <c r="H37">
+        <v>24.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>4.69</v>
+      </c>
+      <c r="K37">
+        <v>0.247</v>
+      </c>
+      <c r="L37">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M37">
+        <v>0.40533262</v>
+      </c>
+      <c r="N37">
+        <v>4.03766738</v>
+      </c>
+      <c r="O37">
+        <v>1.006994244572001</v>
+      </c>
+      <c r="P37">
+        <v>3.030673135428</v>
+      </c>
+      <c r="Q37">
+        <v>3.277673135428</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1605725629201284</v>
+      </c>
+      <c r="T37">
+        <v>2.058972184393329</v>
+      </c>
+      <c r="U37">
+        <v>0.0473</v>
+      </c>
+      <c r="V37">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W37">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>10.96136797477588</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1165490976768283</v>
+      </c>
+      <c r="C38">
+        <v>16.55998926179695</v>
+      </c>
+      <c r="D38">
+        <v>18.63422926179695</v>
+      </c>
+      <c r="E38">
+        <v>8.530239999999999</v>
+      </c>
+      <c r="F38">
+        <v>8.81424</v>
+      </c>
+      <c r="G38">
+        <v>6.74</v>
+      </c>
+      <c r="H38">
+        <v>24.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>4.69</v>
+      </c>
+      <c r="K38">
+        <v>0.247</v>
+      </c>
+      <c r="L38">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M38">
+        <v>0.416913552</v>
+      </c>
+      <c r="N38">
+        <v>4.026086448000001</v>
+      </c>
+      <c r="O38">
+        <v>1.004105960131201</v>
+      </c>
+      <c r="P38">
+        <v>3.0219804878688</v>
+      </c>
+      <c r="Q38">
+        <v>3.2689804878688</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1621373138700442</v>
+      </c>
+      <c r="T38">
+        <v>2.085429529168874</v>
+      </c>
+      <c r="U38">
+        <v>0.0473</v>
+      </c>
+      <c r="V38">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W38">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>10.6568855310321</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1162998464555731</v>
+      </c>
+      <c r="C39">
+        <v>16.3418156409415</v>
+      </c>
+      <c r="D39">
+        <v>18.6608956409415</v>
+      </c>
+      <c r="E39">
+        <v>8.775079999999999</v>
+      </c>
+      <c r="F39">
+        <v>9.05908</v>
+      </c>
+      <c r="G39">
+        <v>6.74</v>
+      </c>
+      <c r="H39">
+        <v>24.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>4.69</v>
+      </c>
+      <c r="K39">
+        <v>0.247</v>
+      </c>
+      <c r="L39">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M39">
+        <v>0.428494484</v>
+      </c>
+      <c r="N39">
+        <v>4.014505516000001</v>
+      </c>
+      <c r="O39">
+        <v>1.001217675690401</v>
+      </c>
+      <c r="P39">
+        <v>3.0132878403096</v>
+      </c>
+      <c r="Q39">
+        <v>3.2602878403096</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1637517394532907</v>
+      </c>
+      <c r="T39">
+        <v>2.11272678965158</v>
+      </c>
+      <c r="U39">
+        <v>0.0473</v>
+      </c>
+      <c r="V39">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W39">
+        <v>0.03550337999999999</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>10.36886159776097</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1171344616343179</v>
+      </c>
+      <c r="C40">
+        <v>16.00798220246073</v>
+      </c>
+      <c r="D40">
+        <v>18.57190220246073</v>
+      </c>
+      <c r="E40">
+        <v>9.019919999999999</v>
+      </c>
+      <c r="F40">
+        <v>9.30392</v>
+      </c>
+      <c r="G40">
+        <v>6.74</v>
+      </c>
+      <c r="H40">
+        <v>24.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>4.69</v>
+      </c>
+      <c r="K40">
+        <v>0.247</v>
+      </c>
+      <c r="L40">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M40">
+        <v>0.475430312</v>
+      </c>
+      <c r="N40">
+        <v>3.967569688000001</v>
+      </c>
+      <c r="O40">
+        <v>0.9895118801872008</v>
+      </c>
+      <c r="P40">
+        <v>2.9780578078128</v>
+      </c>
+      <c r="Q40">
+        <v>3.2250578078128</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.165418243281158</v>
+      </c>
+      <c r="T40">
+        <v>2.14090460692405</v>
+      </c>
+      <c r="U40">
+        <v>0.0511</v>
+      </c>
+      <c r="V40">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W40">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>9.345218190463214</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1169137332130627</v>
+      </c>
+      <c r="C41">
+        <v>15.78659539475051</v>
+      </c>
+      <c r="D41">
+        <v>18.59535539475051</v>
+      </c>
+      <c r="E41">
+        <v>9.264759999999999</v>
+      </c>
+      <c r="F41">
+        <v>9.54876</v>
+      </c>
+      <c r="G41">
+        <v>6.74</v>
+      </c>
+      <c r="H41">
+        <v>24.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>4.69</v>
+      </c>
+      <c r="K41">
+        <v>0.247</v>
+      </c>
+      <c r="L41">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M41">
+        <v>0.487941636</v>
+      </c>
+      <c r="N41">
+        <v>3.955058364000001</v>
+      </c>
+      <c r="O41">
+        <v>0.9863915559816009</v>
+      </c>
+      <c r="P41">
+        <v>2.9686668080184</v>
+      </c>
+      <c r="Q41">
+        <v>3.215666808018399</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1671393865787914</v>
+      </c>
+      <c r="T41">
+        <v>2.170006287057913</v>
+      </c>
+      <c r="U41">
+        <v>0.0511</v>
+      </c>
+      <c r="V41">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W41">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>9.105597211220568</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1166930047918076</v>
+      </c>
+      <c r="C42">
+        <v>15.56526789682174</v>
+      </c>
+      <c r="D42">
+        <v>18.61886789682174</v>
+      </c>
+      <c r="E42">
+        <v>9.509599999999999</v>
+      </c>
+      <c r="F42">
+        <v>9.7936</v>
+      </c>
+      <c r="G42">
+        <v>6.74</v>
+      </c>
+      <c r="H42">
+        <v>24.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>4.69</v>
+      </c>
+      <c r="K42">
+        <v>0.247</v>
+      </c>
+      <c r="L42">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M42">
+        <v>0.5004529599999999</v>
+      </c>
+      <c r="N42">
+        <v>3.94254704</v>
+      </c>
+      <c r="O42">
+        <v>0.9832712317760008</v>
+      </c>
+      <c r="P42">
+        <v>2.959275808224</v>
+      </c>
+      <c r="Q42">
+        <v>3.206275808223999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1689179013196793</v>
+      </c>
+      <c r="T42">
+        <v>2.200078023196238</v>
+      </c>
+      <c r="U42">
+        <v>0.0511</v>
+      </c>
+      <c r="V42">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W42">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>8.877957280940052</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1164722763705524</v>
+      </c>
+      <c r="C43">
+        <v>15.34399993393824</v>
+      </c>
+      <c r="D43">
+        <v>18.64243993393825</v>
+      </c>
+      <c r="E43">
+        <v>9.754439999999999</v>
+      </c>
+      <c r="F43">
+        <v>10.03844</v>
+      </c>
+      <c r="G43">
+        <v>6.74</v>
+      </c>
+      <c r="H43">
+        <v>24.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>4.69</v>
+      </c>
+      <c r="K43">
+        <v>0.247</v>
+      </c>
+      <c r="L43">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M43">
+        <v>0.5129642839999999</v>
+      </c>
+      <c r="N43">
+        <v>3.930035716000001</v>
+      </c>
+      <c r="O43">
+        <v>0.9801509075704009</v>
+      </c>
+      <c r="P43">
+        <v>2.9498848084296</v>
+      </c>
+      <c r="Q43">
+        <v>3.1968848084296</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1707567046958515</v>
+      </c>
+      <c r="T43">
+        <v>2.231169140220608</v>
+      </c>
+      <c r="U43">
+        <v>0.0511</v>
+      </c>
+      <c r="V43">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W43">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>8.66142173750249</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1162515479492972</v>
+      </c>
+      <c r="C44">
+        <v>15.12279173250604</v>
+      </c>
+      <c r="D44">
+        <v>18.66607173250604</v>
+      </c>
+      <c r="E44">
+        <v>9.999279999999999</v>
+      </c>
+      <c r="F44">
+        <v>10.28328</v>
+      </c>
+      <c r="G44">
+        <v>6.74</v>
+      </c>
+      <c r="H44">
+        <v>24.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>4.69</v>
+      </c>
+      <c r="K44">
+        <v>0.247</v>
+      </c>
+      <c r="L44">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M44">
+        <v>0.5254756079999999</v>
+      </c>
+      <c r="N44">
+        <v>3.917524392000001</v>
+      </c>
+      <c r="O44">
+        <v>0.9770305833648009</v>
+      </c>
+      <c r="P44">
+        <v>2.9404938086352</v>
+      </c>
+      <c r="Q44">
+        <v>3.1874938086352</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1726589150849951</v>
+      </c>
+      <c r="T44">
+        <v>2.263332364728576</v>
+      </c>
+      <c r="U44">
+        <v>0.0511</v>
+      </c>
+      <c r="V44">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W44">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>8.455197410419098</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.116030819528042</v>
+      </c>
+      <c r="C45">
+        <v>14.90164352008058</v>
+      </c>
+      <c r="D45">
+        <v>18.68976352008059</v>
+      </c>
+      <c r="E45">
+        <v>10.24412</v>
+      </c>
+      <c r="F45">
+        <v>10.52812</v>
+      </c>
+      <c r="G45">
+        <v>6.74</v>
+      </c>
+      <c r="H45">
+        <v>24.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>4.69</v>
+      </c>
+      <c r="K45">
+        <v>0.247</v>
+      </c>
+      <c r="L45">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M45">
+        <v>0.5379869319999999</v>
+      </c>
+      <c r="N45">
+        <v>3.905013068000001</v>
+      </c>
+      <c r="O45">
+        <v>0.9739102591592008</v>
+      </c>
+      <c r="P45">
+        <v>2.9311028088408</v>
+      </c>
+      <c r="Q45">
+        <v>3.1781028088408</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1746278696983193</v>
+      </c>
+      <c r="T45">
+        <v>2.296624123429806</v>
+      </c>
+      <c r="U45">
+        <v>0.0511</v>
+      </c>
+      <c r="V45">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W45">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>8.258564912502376</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1158100911067868</v>
+      </c>
+      <c r="C46">
+        <v>14.68055552537413</v>
+      </c>
+      <c r="D46">
+        <v>18.71351552537413</v>
+      </c>
+      <c r="E46">
+        <v>10.48896</v>
+      </c>
+      <c r="F46">
+        <v>10.77296</v>
+      </c>
+      <c r="G46">
+        <v>6.74</v>
+      </c>
+      <c r="H46">
+        <v>24.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>4.69</v>
+      </c>
+      <c r="K46">
+        <v>0.247</v>
+      </c>
+      <c r="L46">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M46">
+        <v>0.550498256</v>
+      </c>
+      <c r="N46">
+        <v>3.892501744</v>
+      </c>
+      <c r="O46">
+        <v>0.9707899349536008</v>
+      </c>
+      <c r="P46">
+        <v>2.9217118090464</v>
+      </c>
+      <c r="Q46">
+        <v>3.1687118090464</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1766671441192622</v>
+      </c>
+      <c r="T46">
+        <v>2.331104873513224</v>
+      </c>
+      <c r="U46">
+        <v>0.0511</v>
+      </c>
+      <c r="V46">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W46">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>8.070870255400047</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1155893626855316</v>
+      </c>
+      <c r="C47">
+        <v>14.45952797826303</v>
+      </c>
+      <c r="D47">
+        <v>18.73732797826303</v>
+      </c>
+      <c r="E47">
+        <v>10.7338</v>
+      </c>
+      <c r="F47">
+        <v>11.0178</v>
+      </c>
+      <c r="G47">
+        <v>6.74</v>
+      </c>
+      <c r="H47">
+        <v>24.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>4.69</v>
+      </c>
+      <c r="K47">
+        <v>0.247</v>
+      </c>
+      <c r="L47">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M47">
+        <v>0.56300958</v>
+      </c>
+      <c r="N47">
+        <v>3.87999042</v>
+      </c>
+      <c r="O47">
+        <v>0.9676696107480007</v>
+      </c>
+      <c r="P47">
+        <v>2.912320809252</v>
+      </c>
+      <c r="Q47">
+        <v>3.159320809252</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1787805739736939</v>
+      </c>
+      <c r="T47">
+        <v>2.36683946905422</v>
+      </c>
+      <c r="U47">
+        <v>0.0511</v>
+      </c>
+      <c r="V47">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W47">
+        <v>0.03835565999999999</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>7.891517583057824</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1160246586642764</v>
+      </c>
+      <c r="C48">
+        <v>14.1677856564452</v>
+      </c>
+      <c r="D48">
+        <v>18.69042565644519</v>
+      </c>
+      <c r="E48">
+        <v>10.97864</v>
+      </c>
+      <c r="F48">
+        <v>11.26264</v>
+      </c>
+      <c r="G48">
+        <v>6.74</v>
+      </c>
+      <c r="H48">
+        <v>24.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>4.69</v>
+      </c>
+      <c r="K48">
+        <v>0.247</v>
+      </c>
+      <c r="L48">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M48">
+        <v>0.59691992</v>
+      </c>
+      <c r="N48">
+        <v>3.846080080000001</v>
+      </c>
+      <c r="O48">
+        <v>0.9592123719520008</v>
+      </c>
+      <c r="P48">
+        <v>2.886867708048</v>
+      </c>
+      <c r="Q48">
+        <v>3.133867708048</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1809722790079193</v>
+      </c>
+      <c r="T48">
+        <v>2.403897568133772</v>
+      </c>
+      <c r="U48">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V48">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W48">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>7.443209467695433</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1158181916430212</v>
+      </c>
+      <c r="C49">
+        <v>13.94516278088713</v>
+      </c>
+      <c r="D49">
+        <v>18.71264278088713</v>
+      </c>
+      <c r="E49">
+        <v>11.22348</v>
+      </c>
+      <c r="F49">
+        <v>11.50748</v>
+      </c>
+      <c r="G49">
+        <v>6.74</v>
+      </c>
+      <c r="H49">
+        <v>24.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>4.69</v>
+      </c>
+      <c r="K49">
+        <v>0.247</v>
+      </c>
+      <c r="L49">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M49">
+        <v>0.60989644</v>
+      </c>
+      <c r="N49">
+        <v>3.833103560000001</v>
+      </c>
+      <c r="O49">
+        <v>0.9559760278640008</v>
+      </c>
+      <c r="P49">
+        <v>2.877127532136</v>
+      </c>
+      <c r="Q49">
+        <v>3.124127532136</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1832466898924929</v>
+      </c>
+      <c r="T49">
+        <v>2.442354086046515</v>
+      </c>
+      <c r="U49">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V49">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W49">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>7.284843308808297</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1156117246217661</v>
+      </c>
+      <c r="C50">
+        <v>13.72259278674161</v>
+      </c>
+      <c r="D50">
+        <v>18.73491278674161</v>
+      </c>
+      <c r="E50">
+        <v>11.46832</v>
+      </c>
+      <c r="F50">
+        <v>11.75232</v>
+      </c>
+      <c r="G50">
+        <v>6.74</v>
+      </c>
+      <c r="H50">
+        <v>24.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>4.69</v>
+      </c>
+      <c r="K50">
+        <v>0.247</v>
+      </c>
+      <c r="L50">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M50">
+        <v>0.62287296</v>
+      </c>
+      <c r="N50">
+        <v>3.82012704</v>
+      </c>
+      <c r="O50">
+        <v>0.9527396837760008</v>
+      </c>
+      <c r="P50">
+        <v>2.867387356224</v>
+      </c>
+      <c r="Q50">
+        <v>3.114387356223999</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1856085781187809</v>
+      </c>
+      <c r="T50">
+        <v>2.482289700802055</v>
+      </c>
+      <c r="U50">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V50">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W50">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>7.13307573987479</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1154052576005109</v>
+      </c>
+      <c r="C51">
+        <v>13.50007586303688</v>
+      </c>
+      <c r="D51">
+        <v>18.75723586303688</v>
+      </c>
+      <c r="E51">
+        <v>11.71316</v>
+      </c>
+      <c r="F51">
+        <v>11.99716</v>
+      </c>
+      <c r="G51">
+        <v>6.74</v>
+      </c>
+      <c r="H51">
+        <v>24.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>4.69</v>
+      </c>
+      <c r="K51">
+        <v>0.247</v>
+      </c>
+      <c r="L51">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M51">
+        <v>0.63584948</v>
+      </c>
+      <c r="N51">
+        <v>3.80715052</v>
+      </c>
+      <c r="O51">
+        <v>0.9495033396880008</v>
+      </c>
+      <c r="P51">
+        <v>2.857647180312</v>
+      </c>
+      <c r="Q51">
+        <v>3.104647180311999</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1880630894127664</v>
+      </c>
+      <c r="T51">
+        <v>2.523791418097028</v>
+      </c>
+      <c r="U51">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V51">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W51">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>6.987502765591631</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1151987905792557</v>
+      </c>
+      <c r="C52">
+        <v>13.27761219970315</v>
+      </c>
+      <c r="D52">
+        <v>18.77961219970315</v>
+      </c>
+      <c r="E52">
+        <v>11.958</v>
+      </c>
+      <c r="F52">
+        <v>12.242</v>
+      </c>
+      <c r="G52">
+        <v>6.74</v>
+      </c>
+      <c r="H52">
+        <v>24.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>4.69</v>
+      </c>
+      <c r="K52">
+        <v>0.247</v>
+      </c>
+      <c r="L52">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M52">
+        <v>0.648826</v>
+      </c>
+      <c r="N52">
+        <v>3.794174</v>
+      </c>
+      <c r="O52">
+        <v>0.9462669956000007</v>
+      </c>
+      <c r="P52">
+        <v>2.8479070044</v>
+      </c>
+      <c r="Q52">
+        <v>3.0949070044</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1906157811585114</v>
+      </c>
+      <c r="T52">
+        <v>2.5669532040838</v>
+      </c>
+      <c r="U52">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V52">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W52">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>6.847752710279798</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1149923235580005</v>
+      </c>
+      <c r="C53">
+        <v>13.05520198757806</v>
+      </c>
+      <c r="D53">
+        <v>18.80204198757806</v>
+      </c>
+      <c r="E53">
+        <v>12.20284</v>
+      </c>
+      <c r="F53">
+        <v>12.48684</v>
+      </c>
+      <c r="G53">
+        <v>6.74</v>
+      </c>
+      <c r="H53">
+        <v>24.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>4.69</v>
+      </c>
+      <c r="K53">
+        <v>0.247</v>
+      </c>
+      <c r="L53">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M53">
+        <v>0.6618025200000001</v>
+      </c>
+      <c r="N53">
+        <v>3.78119748</v>
+      </c>
+      <c r="O53">
+        <v>0.9430306515120007</v>
+      </c>
+      <c r="P53">
+        <v>2.838166828488</v>
+      </c>
+      <c r="Q53">
+        <v>3.085166828488</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1932726644040827</v>
+      </c>
+      <c r="T53">
+        <v>2.611876695621053</v>
+      </c>
+      <c r="U53">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V53">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W53">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>6.713483049293919</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1147858565367453</v>
+      </c>
+      <c r="C54">
+        <v>12.83284541841203</v>
+      </c>
+      <c r="D54">
+        <v>18.82452541841202</v>
+      </c>
+      <c r="E54">
+        <v>12.44768</v>
+      </c>
+      <c r="F54">
+        <v>12.73168</v>
+      </c>
+      <c r="G54">
+        <v>6.74</v>
+      </c>
+      <c r="H54">
+        <v>24.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>4.69</v>
+      </c>
+      <c r="K54">
+        <v>0.247</v>
+      </c>
+      <c r="L54">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M54">
+        <v>0.67477904</v>
+      </c>
+      <c r="N54">
+        <v>3.768220960000001</v>
+      </c>
+      <c r="O54">
+        <v>0.9397943074240008</v>
+      </c>
+      <c r="P54">
+        <v>2.828426652576</v>
+      </c>
+      <c r="Q54">
+        <v>3.075426652576</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1960402511182194</v>
+      </c>
+      <c r="T54">
+        <v>2.658671999305691</v>
+      </c>
+      <c r="U54">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V54">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W54">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>6.584377606038268</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1145793895154902</v>
+      </c>
+      <c r="C55">
+        <v>12.61054268487377</v>
+      </c>
+      <c r="D55">
+        <v>18.84706268487376</v>
+      </c>
+      <c r="E55">
+        <v>12.69252</v>
+      </c>
+      <c r="F55">
+        <v>12.97652</v>
+      </c>
+      <c r="G55">
+        <v>6.74</v>
+      </c>
+      <c r="H55">
+        <v>24.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>4.69</v>
+      </c>
+      <c r="K55">
+        <v>0.247</v>
+      </c>
+      <c r="L55">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M55">
+        <v>0.68775556</v>
+      </c>
+      <c r="N55">
+        <v>3.75524444</v>
+      </c>
+      <c r="O55">
+        <v>0.9365579633360007</v>
+      </c>
+      <c r="P55">
+        <v>2.818686476663999</v>
+      </c>
+      <c r="Q55">
+        <v>3.065686476663999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1989256074797663</v>
+      </c>
+      <c r="T55">
+        <v>2.707458592508824</v>
+      </c>
+      <c r="U55">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V55">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W55">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>6.460144066301696</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.114372922494235</v>
+      </c>
+      <c r="C56">
+        <v>12.38829398055575</v>
+      </c>
+      <c r="D56">
+        <v>18.86965398055575</v>
+      </c>
+      <c r="E56">
+        <v>12.93736</v>
+      </c>
+      <c r="F56">
+        <v>13.22136</v>
+      </c>
+      <c r="G56">
+        <v>6.74</v>
+      </c>
+      <c r="H56">
+        <v>24.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>4.69</v>
+      </c>
+      <c r="K56">
+        <v>0.247</v>
+      </c>
+      <c r="L56">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M56">
+        <v>0.7007320800000001</v>
+      </c>
+      <c r="N56">
+        <v>3.742267920000001</v>
+      </c>
+      <c r="O56">
+        <v>0.9333216192480008</v>
+      </c>
+      <c r="P56">
+        <v>2.808946300752</v>
+      </c>
+      <c r="Q56">
+        <v>3.055946300752</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2019364141179021</v>
+      </c>
+      <c r="T56">
+        <v>2.758366341938181</v>
+      </c>
+      <c r="U56">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V56">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W56">
+        <v>0.03978179999999999</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>6.34051176877759</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1149921154729798</v>
+      </c>
+      <c r="C57">
+        <v>12.07586462016584</v>
+      </c>
+      <c r="D57">
+        <v>18.80206462016584</v>
+      </c>
+      <c r="E57">
+        <v>13.1822</v>
+      </c>
+      <c r="F57">
+        <v>13.4662</v>
+      </c>
+      <c r="G57">
+        <v>6.74</v>
+      </c>
+      <c r="H57">
+        <v>24.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>4.69</v>
+      </c>
+      <c r="K57">
+        <v>0.247</v>
+      </c>
+      <c r="L57">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M57">
+        <v>0.740641</v>
+      </c>
+      <c r="N57">
+        <v>3.702359</v>
+      </c>
+      <c r="O57">
+        <v>0.9233683346000008</v>
+      </c>
+      <c r="P57">
+        <v>2.778990665399999</v>
+      </c>
+      <c r="Q57">
+        <v>3.025990665399999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2050810343843995</v>
+      </c>
+      <c r="T57">
+        <v>2.811536658008842</v>
+      </c>
+      <c r="U57">
+        <v>0.055</v>
+      </c>
+      <c r="V57">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W57">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>5.998857746195526</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1148006604517246</v>
+      </c>
+      <c r="C58">
+        <v>11.85187154206809</v>
+      </c>
+      <c r="D58">
+        <v>18.82291154206808</v>
+      </c>
+      <c r="E58">
+        <v>13.42704</v>
+      </c>
+      <c r="F58">
+        <v>13.71104</v>
+      </c>
+      <c r="G58">
+        <v>6.74</v>
+      </c>
+      <c r="H58">
+        <v>24.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>4.69</v>
+      </c>
+      <c r="K58">
+        <v>0.247</v>
+      </c>
+      <c r="L58">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M58">
+        <v>0.7541072000000001</v>
+      </c>
+      <c r="N58">
+        <v>3.688892800000001</v>
+      </c>
+      <c r="O58">
+        <v>0.9200098643200008</v>
+      </c>
+      <c r="P58">
+        <v>2.76888293568</v>
+      </c>
+      <c r="Q58">
+        <v>3.01588293568</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2083685919357377</v>
+      </c>
+      <c r="T58">
+        <v>2.867123806628169</v>
+      </c>
+      <c r="U58">
+        <v>0.055</v>
+      </c>
+      <c r="V58">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W58">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>5.891735286442034</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1146092054304694</v>
+      </c>
+      <c r="C59">
+        <v>11.62792474362692</v>
+      </c>
+      <c r="D59">
+        <v>18.84380474362692</v>
+      </c>
+      <c r="E59">
+        <v>13.67188</v>
+      </c>
+      <c r="F59">
+        <v>13.95588</v>
+      </c>
+      <c r="G59">
+        <v>6.74</v>
+      </c>
+      <c r="H59">
+        <v>24.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>4.69</v>
+      </c>
+      <c r="K59">
+        <v>0.247</v>
+      </c>
+      <c r="L59">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M59">
+        <v>0.7675734000000001</v>
+      </c>
+      <c r="N59">
+        <v>3.675426600000001</v>
+      </c>
+      <c r="O59">
+        <v>0.9166513940400008</v>
+      </c>
+      <c r="P59">
+        <v>2.75877520596</v>
+      </c>
+      <c r="Q59">
+        <v>3.00577520596</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2118090591406266</v>
+      </c>
+      <c r="T59">
+        <v>2.925296404020489</v>
+      </c>
+      <c r="U59">
+        <v>0.055</v>
+      </c>
+      <c r="V59">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W59">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>5.788371509486911</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1144177504092142</v>
+      </c>
+      <c r="C60">
+        <v>11.40402437912318</v>
+      </c>
+      <c r="D60">
+        <v>18.86474437912317</v>
+      </c>
+      <c r="E60">
+        <v>13.91672</v>
+      </c>
+      <c r="F60">
+        <v>14.20072</v>
+      </c>
+      <c r="G60">
+        <v>6.74</v>
+      </c>
+      <c r="H60">
+        <v>24.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>4.69</v>
+      </c>
+      <c r="K60">
+        <v>0.247</v>
+      </c>
+      <c r="L60">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M60">
+        <v>0.7810395999999999</v>
+      </c>
+      <c r="N60">
+        <v>3.661960400000001</v>
+      </c>
+      <c r="O60">
+        <v>0.9132929237600008</v>
+      </c>
+      <c r="P60">
+        <v>2.74866747624</v>
+      </c>
+      <c r="Q60">
+        <v>2.99566747624</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2154133581171767</v>
+      </c>
+      <c r="T60">
+        <v>2.986239125098157</v>
+      </c>
+      <c r="U60">
+        <v>0.055</v>
+      </c>
+      <c r="V60">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W60">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>5.688572000702655</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.114226295387959</v>
+      </c>
+      <c r="C61">
+        <v>11.18017060352417</v>
+      </c>
+      <c r="D61">
+        <v>18.88573060352417</v>
+      </c>
+      <c r="E61">
+        <v>14.16156</v>
+      </c>
+      <c r="F61">
+        <v>14.44556</v>
+      </c>
+      <c r="G61">
+        <v>6.74</v>
+      </c>
+      <c r="H61">
+        <v>24.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>4.69</v>
+      </c>
+      <c r="K61">
+        <v>0.247</v>
+      </c>
+      <c r="L61">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M61">
+        <v>0.7945057999999999</v>
+      </c>
+      <c r="N61">
+        <v>3.6484942</v>
+      </c>
+      <c r="O61">
+        <v>0.9099344534800008</v>
+      </c>
+      <c r="P61">
+        <v>2.73855974652</v>
+      </c>
+      <c r="Q61">
+        <v>2.985559746519999</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2191934765559976</v>
+      </c>
+      <c r="T61">
+        <v>3.05015466183815</v>
+      </c>
+      <c r="U61">
+        <v>0.055</v>
+      </c>
+      <c r="V61">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W61">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>5.592155526114474</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1140348403667038</v>
+      </c>
+      <c r="C62">
+        <v>10.95636357248757</v>
+      </c>
+      <c r="D62">
+        <v>18.90676357248757</v>
+      </c>
+      <c r="E62">
+        <v>14.4064</v>
+      </c>
+      <c r="F62">
+        <v>14.6904</v>
+      </c>
+      <c r="G62">
+        <v>6.74</v>
+      </c>
+      <c r="H62">
+        <v>24.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>4.69</v>
+      </c>
+      <c r="K62">
+        <v>0.247</v>
+      </c>
+      <c r="L62">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M62">
+        <v>0.8079719999999999</v>
+      </c>
+      <c r="N62">
+        <v>3.635028000000001</v>
+      </c>
+      <c r="O62">
+        <v>0.9065759832000008</v>
+      </c>
+      <c r="P62">
+        <v>2.7284520168</v>
+      </c>
+      <c r="Q62">
+        <v>2.9754520168</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2231626009167596</v>
+      </c>
+      <c r="T62">
+        <v>3.117265975415143</v>
+      </c>
+      <c r="U62">
+        <v>0.055</v>
+      </c>
+      <c r="V62">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W62">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>5.498952934012566</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1138433853454487</v>
+      </c>
+      <c r="C63">
+        <v>10.73260344236526</v>
+      </c>
+      <c r="D63">
+        <v>18.92784344236526</v>
+      </c>
+      <c r="E63">
+        <v>14.65124</v>
+      </c>
+      <c r="F63">
+        <v>14.93524</v>
+      </c>
+      <c r="G63">
+        <v>6.74</v>
+      </c>
+      <c r="H63">
+        <v>24.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>4.69</v>
+      </c>
+      <c r="K63">
+        <v>0.247</v>
+      </c>
+      <c r="L63">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M63">
+        <v>0.8214381999999999</v>
+      </c>
+      <c r="N63">
+        <v>3.621561800000001</v>
+      </c>
+      <c r="O63">
+        <v>0.9032175129200009</v>
+      </c>
+      <c r="P63">
+        <v>2.71834428708</v>
+      </c>
+      <c r="Q63">
+        <v>2.96534428708</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.227335270116535</v>
+      </c>
+      <c r="T63">
+        <v>3.187818894816598</v>
+      </c>
+      <c r="U63">
+        <v>0.055</v>
+      </c>
+      <c r="V63">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W63">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>5.408806164602524</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1136519303241935</v>
+      </c>
+      <c r="C64">
+        <v>10.50889037020719</v>
+      </c>
+      <c r="D64">
+        <v>18.94897037020719</v>
+      </c>
+      <c r="E64">
+        <v>14.89608</v>
+      </c>
+      <c r="F64">
+        <v>15.18008</v>
+      </c>
+      <c r="G64">
+        <v>6.74</v>
+      </c>
+      <c r="H64">
+        <v>24.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>4.69</v>
+      </c>
+      <c r="K64">
+        <v>0.247</v>
+      </c>
+      <c r="L64">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M64">
+        <v>0.8349043999999999</v>
+      </c>
+      <c r="N64">
+        <v>3.6080956</v>
+      </c>
+      <c r="O64">
+        <v>0.8998590426400007</v>
+      </c>
+      <c r="P64">
+        <v>2.70823655736</v>
+      </c>
+      <c r="Q64">
+        <v>2.95523655736</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2317275534847197</v>
+      </c>
+      <c r="T64">
+        <v>3.262085125765497</v>
+      </c>
+      <c r="U64">
+        <v>0.055</v>
+      </c>
+      <c r="V64">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W64">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>5.321567355496032</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1134604753029383</v>
+      </c>
+      <c r="C65">
+        <v>10.28522451376525</v>
+      </c>
+      <c r="D65">
+        <v>18.97014451376525</v>
+      </c>
+      <c r="E65">
+        <v>15.14092</v>
+      </c>
+      <c r="F65">
+        <v>15.42492</v>
+      </c>
+      <c r="G65">
+        <v>6.74</v>
+      </c>
+      <c r="H65">
+        <v>24.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>4.69</v>
+      </c>
+      <c r="K65">
+        <v>0.247</v>
+      </c>
+      <c r="L65">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M65">
+        <v>0.8483705999999999</v>
+      </c>
+      <c r="N65">
+        <v>3.594629400000001</v>
+      </c>
+      <c r="O65">
+        <v>0.8965005723600008</v>
+      </c>
+      <c r="P65">
+        <v>2.69812882764</v>
+      </c>
+      <c r="Q65">
+        <v>2.94512882764</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2363572575755089</v>
+      </c>
+      <c r="T65">
+        <v>3.340365747576499</v>
+      </c>
+      <c r="U65">
+        <v>0.055</v>
+      </c>
+      <c r="V65">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W65">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>5.23709803239292</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1132690202816831</v>
+      </c>
+      <c r="C66">
+        <v>10.06160603149726</v>
+      </c>
+      <c r="D66">
+        <v>18.99136603149726</v>
+      </c>
+      <c r="E66">
+        <v>15.38576</v>
+      </c>
+      <c r="F66">
+        <v>15.66976</v>
+      </c>
+      <c r="G66">
+        <v>6.74</v>
+      </c>
+      <c r="H66">
+        <v>24.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>4.69</v>
+      </c>
+      <c r="K66">
+        <v>0.247</v>
+      </c>
+      <c r="L66">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M66">
+        <v>0.8618368</v>
+      </c>
+      <c r="N66">
+        <v>3.581163200000001</v>
+      </c>
+      <c r="O66">
+        <v>0.8931421020800008</v>
+      </c>
+      <c r="P66">
+        <v>2.68802109792</v>
+      </c>
+      <c r="Q66">
+        <v>2.93502109792</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2412441674491197</v>
+      </c>
+      <c r="T66">
+        <v>3.422995292821446</v>
+      </c>
+      <c r="U66">
+        <v>0.055</v>
+      </c>
+      <c r="V66">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W66">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>5.155268375636781</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1130775652604279</v>
+      </c>
+      <c r="C67">
+        <v>9.838035082570862</v>
+      </c>
+      <c r="D67">
+        <v>19.01263508257086</v>
+      </c>
+      <c r="E67">
+        <v>15.6306</v>
+      </c>
+      <c r="F67">
+        <v>15.9146</v>
+      </c>
+      <c r="G67">
+        <v>6.74</v>
+      </c>
+      <c r="H67">
+        <v>24.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>4.69</v>
+      </c>
+      <c r="K67">
+        <v>0.247</v>
+      </c>
+      <c r="L67">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M67">
+        <v>0.8753030000000001</v>
+      </c>
+      <c r="N67">
+        <v>3.567697</v>
+      </c>
+      <c r="O67">
+        <v>0.8897836318000008</v>
+      </c>
+      <c r="P67">
+        <v>2.6779133682</v>
+      </c>
+      <c r="Q67">
+        <v>2.924913368199999</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2464103293155084</v>
+      </c>
+      <c r="T67">
+        <v>3.510346526366104</v>
+      </c>
+      <c r="U67">
+        <v>0.055</v>
+      </c>
+      <c r="V67">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W67">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>5.075956554473136</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1128861102391727</v>
+      </c>
+      <c r="C68">
+        <v>9.614511826867552</v>
+      </c>
+      <c r="D68">
+        <v>19.03395182686755</v>
+      </c>
+      <c r="E68">
+        <v>15.87544</v>
+      </c>
+      <c r="F68">
+        <v>16.15944</v>
+      </c>
+      <c r="G68">
+        <v>6.74</v>
+      </c>
+      <c r="H68">
+        <v>24.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>4.69</v>
+      </c>
+      <c r="K68">
+        <v>0.247</v>
+      </c>
+      <c r="L68">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M68">
+        <v>0.8887692</v>
+      </c>
+      <c r="N68">
+        <v>3.5542308</v>
+      </c>
+      <c r="O68">
+        <v>0.8864251615200007</v>
+      </c>
+      <c r="P68">
+        <v>2.66780563848</v>
+      </c>
+      <c r="Q68">
+        <v>2.91480563848</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2518803830563904</v>
+      </c>
+      <c r="T68">
+        <v>3.602836067766329</v>
+      </c>
+      <c r="U68">
+        <v>0.055</v>
+      </c>
+      <c r="V68">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W68">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>4.999048121829604</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1126946552179175</v>
+      </c>
+      <c r="C69">
+        <v>9.39103642498663</v>
+      </c>
+      <c r="D69">
+        <v>19.05531642498663</v>
+      </c>
+      <c r="E69">
+        <v>16.12028</v>
+      </c>
+      <c r="F69">
+        <v>16.40428</v>
+      </c>
+      <c r="G69">
+        <v>6.74</v>
+      </c>
+      <c r="H69">
+        <v>24.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>4.69</v>
+      </c>
+      <c r="K69">
+        <v>0.247</v>
+      </c>
+      <c r="L69">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M69">
+        <v>0.9022354</v>
+      </c>
+      <c r="N69">
+        <v>3.540764600000001</v>
+      </c>
+      <c r="O69">
+        <v>0.8830666912400008</v>
+      </c>
+      <c r="P69">
+        <v>2.65769790876</v>
+      </c>
+      <c r="Q69">
+        <v>2.90469790876</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2576819552058108</v>
+      </c>
+      <c r="T69">
+        <v>3.700931035918084</v>
+      </c>
+      <c r="U69">
+        <v>0.055</v>
+      </c>
+      <c r="V69">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W69">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>4.924435463294834</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1125032001966624</v>
+      </c>
+      <c r="C70">
+        <v>9.167609038249292</v>
+      </c>
+      <c r="D70">
+        <v>19.07672903824929</v>
+      </c>
+      <c r="E70">
+        <v>16.36512</v>
+      </c>
+      <c r="F70">
+        <v>16.64912</v>
+      </c>
+      <c r="G70">
+        <v>6.74</v>
+      </c>
+      <c r="H70">
+        <v>24.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>4.69</v>
+      </c>
+      <c r="K70">
+        <v>0.247</v>
+      </c>
+      <c r="L70">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M70">
+        <v>0.9157016</v>
+      </c>
+      <c r="N70">
+        <v>3.5272984</v>
+      </c>
+      <c r="O70">
+        <v>0.8797082209600007</v>
+      </c>
+      <c r="P70">
+        <v>2.64759017904</v>
+      </c>
+      <c r="Q70">
+        <v>2.89459017904</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2638461256145699</v>
+      </c>
+      <c r="T70">
+        <v>3.805156939579323</v>
+      </c>
+      <c r="U70">
+        <v>0.055</v>
+      </c>
+      <c r="V70">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W70">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>4.852017294716969</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1123117451754072</v>
+      </c>
+      <c r="C71">
+        <v>8.944229828702639</v>
+      </c>
+      <c r="D71">
+        <v>19.09818982870264</v>
+      </c>
+      <c r="E71">
+        <v>16.60996</v>
+      </c>
+      <c r="F71">
+        <v>16.89396</v>
+      </c>
+      <c r="G71">
+        <v>6.74</v>
+      </c>
+      <c r="H71">
+        <v>24.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>4.69</v>
+      </c>
+      <c r="K71">
+        <v>0.247</v>
+      </c>
+      <c r="L71">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M71">
+        <v>0.9291678</v>
+      </c>
+      <c r="N71">
+        <v>3.5138322</v>
+      </c>
+      <c r="O71">
+        <v>0.8763497506800008</v>
+      </c>
+      <c r="P71">
+        <v>2.63748244932</v>
+      </c>
+      <c r="Q71">
+        <v>2.88448244932</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2704079844367974</v>
+      </c>
+      <c r="T71">
+        <v>3.916107095089675</v>
+      </c>
+      <c r="U71">
+        <v>0.055</v>
+      </c>
+      <c r="V71">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W71">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>4.781698203489187</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.112120290154152</v>
+      </c>
+      <c r="C72">
+        <v>8.720898959123804</v>
+      </c>
+      <c r="D72">
+        <v>19.1196989591238</v>
+      </c>
+      <c r="E72">
+        <v>16.8548</v>
+      </c>
+      <c r="F72">
+        <v>17.1388</v>
+      </c>
+      <c r="G72">
+        <v>6.74</v>
+      </c>
+      <c r="H72">
+        <v>24.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>4.69</v>
+      </c>
+      <c r="K72">
+        <v>0.247</v>
+      </c>
+      <c r="L72">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M72">
+        <v>0.942634</v>
+      </c>
+      <c r="N72">
+        <v>3.500366000000001</v>
+      </c>
+      <c r="O72">
+        <v>0.8729912804000007</v>
+      </c>
+      <c r="P72">
+        <v>2.6273747196</v>
+      </c>
+      <c r="Q72">
+        <v>2.8743747196</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.27740730051384</v>
+      </c>
+      <c r="T72">
+        <v>4.034453927634051</v>
+      </c>
+      <c r="U72">
+        <v>0.055</v>
+      </c>
+      <c r="V72">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W72">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>4.713388229153628</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1119288351328968</v>
+      </c>
+      <c r="C73">
+        <v>8.497616593024031</v>
+      </c>
+      <c r="D73">
+        <v>19.14125659302402</v>
+      </c>
+      <c r="E73">
+        <v>17.09964</v>
+      </c>
+      <c r="F73">
+        <v>17.38364</v>
+      </c>
+      <c r="G73">
+        <v>6.74</v>
+      </c>
+      <c r="H73">
+        <v>24.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>4.69</v>
+      </c>
+      <c r="K73">
+        <v>0.247</v>
+      </c>
+      <c r="L73">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M73">
+        <v>0.9561001999999998</v>
+      </c>
+      <c r="N73">
+        <v>3.486899800000001</v>
+      </c>
+      <c r="O73">
+        <v>0.8696328101200008</v>
+      </c>
+      <c r="P73">
+        <v>2.61726698988</v>
+      </c>
+      <c r="Q73">
+        <v>2.86426698988</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2848893280444718</v>
+      </c>
+      <c r="T73">
+        <v>4.160962610698726</v>
+      </c>
+      <c r="U73">
+        <v>0.055</v>
+      </c>
+      <c r="V73">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W73">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>4.64700247944724</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1117373801116416</v>
+      </c>
+      <c r="C74">
+        <v>8.274382894652856</v>
+      </c>
+      <c r="D74">
+        <v>19.16286289465286</v>
+      </c>
+      <c r="E74">
+        <v>17.34448</v>
+      </c>
+      <c r="F74">
+        <v>17.62848</v>
+      </c>
+      <c r="G74">
+        <v>6.74</v>
+      </c>
+      <c r="H74">
+        <v>24.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>4.69</v>
+      </c>
+      <c r="K74">
+        <v>0.247</v>
+      </c>
+      <c r="L74">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M74">
+        <v>0.9695663999999999</v>
+      </c>
+      <c r="N74">
+        <v>3.473433600000001</v>
+      </c>
+      <c r="O74">
+        <v>0.8662743398400008</v>
+      </c>
+      <c r="P74">
+        <v>2.60715926016</v>
+      </c>
+      <c r="Q74">
+        <v>2.85415926016</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2929057861130057</v>
+      </c>
+      <c r="T74">
+        <v>4.296507628268022</v>
+      </c>
+      <c r="U74">
+        <v>0.055</v>
+      </c>
+      <c r="V74">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W74">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>4.582460778343805</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.1115459250903864</v>
+      </c>
+      <c r="C75">
+        <v>8.051198029002258</v>
+      </c>
+      <c r="D75">
+        <v>19.18451802900226</v>
+      </c>
+      <c r="E75">
+        <v>17.58932</v>
+      </c>
+      <c r="F75">
+        <v>17.87332</v>
+      </c>
+      <c r="G75">
+        <v>6.74</v>
+      </c>
+      <c r="H75">
+        <v>24.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>4.69</v>
+      </c>
+      <c r="K75">
+        <v>0.247</v>
+      </c>
+      <c r="L75">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M75">
+        <v>0.9830326</v>
+      </c>
+      <c r="N75">
+        <v>3.4599674</v>
+      </c>
+      <c r="O75">
+        <v>0.8629158695600008</v>
+      </c>
+      <c r="P75">
+        <v>2.59705153044</v>
+      </c>
+      <c r="Q75">
+        <v>2.84405153044</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3015160558903201</v>
+      </c>
+      <c r="T75">
+        <v>4.442093017509118</v>
+      </c>
+      <c r="U75">
+        <v>0.055</v>
+      </c>
+      <c r="V75">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W75">
+        <v>0.04128299999999999</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>4.519687343024026</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.1134651572691312</v>
+      </c>
+      <c r="C76">
+        <v>7.591466142975744</v>
+      </c>
+      <c r="D76">
+        <v>18.96962614297574</v>
+      </c>
+      <c r="E76">
+        <v>17.83416</v>
+      </c>
+      <c r="F76">
+        <v>18.11816</v>
+      </c>
+      <c r="G76">
+        <v>6.74</v>
+      </c>
+      <c r="H76">
+        <v>24.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>4.69</v>
+      </c>
+      <c r="K76">
+        <v>0.247</v>
+      </c>
+      <c r="L76">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M76">
+        <v>1.065347808</v>
+      </c>
+      <c r="N76">
+        <v>3.377652192</v>
+      </c>
+      <c r="O76">
+        <v>0.8423864566848006</v>
+      </c>
+      <c r="P76">
+        <v>2.5352657353152</v>
+      </c>
+      <c r="Q76">
+        <v>2.7822657353152</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3107886541120433</v>
+      </c>
+      <c r="T76">
+        <v>4.598877282845684</v>
+      </c>
+      <c r="U76">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V76">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W76">
+        <v>0.04413527999999999</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>4.170468992976986</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.113302225047876</v>
+      </c>
+      <c r="C77">
+        <v>7.36468210107639</v>
+      </c>
+      <c r="D77">
+        <v>18.98768210107639</v>
+      </c>
+      <c r="E77">
+        <v>18.079</v>
+      </c>
+      <c r="F77">
+        <v>18.363</v>
+      </c>
+      <c r="G77">
+        <v>6.74</v>
+      </c>
+      <c r="H77">
+        <v>24.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>4.69</v>
+      </c>
+      <c r="K77">
+        <v>0.247</v>
+      </c>
+      <c r="L77">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M77">
+        <v>1.0797444</v>
+      </c>
+      <c r="N77">
+        <v>3.3632556</v>
+      </c>
+      <c r="O77">
+        <v>0.8387959466400007</v>
+      </c>
+      <c r="P77">
+        <v>2.52445965336</v>
+      </c>
+      <c r="Q77">
+        <v>2.77145965336</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3208030601915042</v>
+      </c>
+      <c r="T77">
+        <v>4.768204289409174</v>
+      </c>
+      <c r="U77">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V77">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W77">
+        <v>0.04413527999999999</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>4.114862739737294</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.1131392928266209</v>
+      </c>
+      <c r="C78">
+        <v>7.137932464518624</v>
+      </c>
+      <c r="D78">
+        <v>19.00577246451862</v>
+      </c>
+      <c r="E78">
+        <v>18.32384</v>
+      </c>
+      <c r="F78">
+        <v>18.60784</v>
+      </c>
+      <c r="G78">
+        <v>6.74</v>
+      </c>
+      <c r="H78">
+        <v>24.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>4.69</v>
+      </c>
+      <c r="K78">
+        <v>0.247</v>
+      </c>
+      <c r="L78">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M78">
+        <v>1.094140992</v>
+      </c>
+      <c r="N78">
+        <v>3.348859008000001</v>
+      </c>
+      <c r="O78">
+        <v>0.8352054365952007</v>
+      </c>
+      <c r="P78">
+        <v>2.5136535714048</v>
+      </c>
+      <c r="Q78">
+        <v>2.7606535714048</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3316520001109203</v>
+      </c>
+      <c r="T78">
+        <v>4.951641879852955</v>
+      </c>
+      <c r="U78">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V78">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W78">
+        <v>0.04413527999999999</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>4.060719808951276</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.1129763606053657</v>
+      </c>
+      <c r="C79">
+        <v>6.911217331734477</v>
+      </c>
+      <c r="D79">
+        <v>19.02389733173448</v>
+      </c>
+      <c r="E79">
+        <v>18.56868</v>
+      </c>
+      <c r="F79">
+        <v>18.85268</v>
+      </c>
+      <c r="G79">
+        <v>6.74</v>
+      </c>
+      <c r="H79">
+        <v>24.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>4.69</v>
+      </c>
+      <c r="K79">
+        <v>0.247</v>
+      </c>
+      <c r="L79">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M79">
+        <v>1.108537584</v>
+      </c>
+      <c r="N79">
+        <v>3.334462416</v>
+      </c>
+      <c r="O79">
+        <v>0.8316149265504007</v>
+      </c>
+      <c r="P79">
+        <v>2.5028474894496</v>
+      </c>
+      <c r="Q79">
+        <v>2.7498474894496</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3434443261102856</v>
+      </c>
+      <c r="T79">
+        <v>5.151030565117935</v>
+      </c>
+      <c r="U79">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V79">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W79">
+        <v>0.04413527999999999</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>4.007983188055805</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.1152723939841105</v>
+      </c>
+      <c r="C80">
+        <v>6.414109140931412</v>
+      </c>
+      <c r="D80">
+        <v>18.77162914093141</v>
+      </c>
+      <c r="E80">
+        <v>18.81352</v>
+      </c>
+      <c r="F80">
+        <v>19.09752</v>
+      </c>
+      <c r="G80">
+        <v>6.74</v>
+      </c>
+      <c r="H80">
+        <v>24.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>4.69</v>
+      </c>
+      <c r="K80">
+        <v>0.247</v>
+      </c>
+      <c r="L80">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M80">
+        <v>1.20314376</v>
+      </c>
+      <c r="N80">
+        <v>3.239856240000001</v>
+      </c>
+      <c r="O80">
+        <v>0.8080201462560008</v>
+      </c>
+      <c r="P80">
+        <v>2.431836093744</v>
+      </c>
+      <c r="Q80">
+        <v>2.678836093744</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3563086817459569</v>
+      </c>
+      <c r="T80">
+        <v>5.368545494497914</v>
+      </c>
+      <c r="U80">
+        <v>0.063</v>
+      </c>
+      <c r="V80">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W80">
+        <v>0.04728779999999999</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>3.692825535661675</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.1151409869628553</v>
+      </c>
+      <c r="C81">
+        <v>6.183526367904605</v>
+      </c>
+      <c r="D81">
+        <v>18.7858863679046</v>
+      </c>
+      <c r="E81">
+        <v>19.05836</v>
+      </c>
+      <c r="F81">
+        <v>19.34236</v>
+      </c>
+      <c r="G81">
+        <v>6.74</v>
+      </c>
+      <c r="H81">
+        <v>24.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>4.69</v>
+      </c>
+      <c r="K81">
+        <v>0.247</v>
+      </c>
+      <c r="L81">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M81">
+        <v>1.21856868</v>
+      </c>
+      <c r="N81">
+        <v>3.224431320000001</v>
+      </c>
+      <c r="O81">
+        <v>0.8041731712080008</v>
+      </c>
+      <c r="P81">
+        <v>2.420258148792</v>
+      </c>
+      <c r="Q81">
+        <v>2.667258148792</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3703982141088349</v>
+      </c>
+      <c r="T81">
+        <v>5.606776131437889</v>
+      </c>
+      <c r="U81">
+        <v>0.063</v>
+      </c>
+      <c r="V81">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W81">
+        <v>0.04728779999999999</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>3.646080908627982</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.1150095799416001</v>
+      </c>
+      <c r="C82">
+        <v>5.952965268332033</v>
+      </c>
+      <c r="D82">
+        <v>18.80016526833203</v>
+      </c>
+      <c r="E82">
+        <v>19.3032</v>
+      </c>
+      <c r="F82">
+        <v>19.5872</v>
+      </c>
+      <c r="G82">
+        <v>6.74</v>
+      </c>
+      <c r="H82">
+        <v>24.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>4.69</v>
+      </c>
+      <c r="K82">
+        <v>0.247</v>
+      </c>
+      <c r="L82">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M82">
+        <v>1.2339936</v>
+      </c>
+      <c r="N82">
+        <v>3.209006400000001</v>
+      </c>
+      <c r="O82">
+        <v>0.8003261961600008</v>
+      </c>
+      <c r="P82">
+        <v>2.40868020384</v>
+      </c>
+      <c r="Q82">
+        <v>2.65568020384</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3858966997080007</v>
+      </c>
+      <c r="T82">
+        <v>5.868829832071862</v>
+      </c>
+      <c r="U82">
+        <v>0.063</v>
+      </c>
+      <c r="V82">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W82">
+        <v>0.04728779999999999</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>3.600504897270132</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.1148781729203449</v>
+      </c>
+      <c r="C83">
+        <v>5.722425891672415</v>
+      </c>
+      <c r="D83">
+        <v>18.81446589167241</v>
+      </c>
+      <c r="E83">
+        <v>19.54804</v>
+      </c>
+      <c r="F83">
+        <v>19.83204</v>
+      </c>
+      <c r="G83">
+        <v>6.74</v>
+      </c>
+      <c r="H83">
+        <v>24.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>4.69</v>
+      </c>
+      <c r="K83">
+        <v>0.247</v>
+      </c>
+      <c r="L83">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M83">
+        <v>1.24941852</v>
+      </c>
+      <c r="N83">
+        <v>3.193581480000001</v>
+      </c>
+      <c r="O83">
+        <v>0.7964792211120008</v>
+      </c>
+      <c r="P83">
+        <v>2.397102258888</v>
+      </c>
+      <c r="Q83">
+        <v>2.644102258888</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4030266048439209</v>
+      </c>
+      <c r="T83">
+        <v>6.15846813277257</v>
+      </c>
+      <c r="U83">
+        <v>0.063</v>
+      </c>
+      <c r="V83">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W83">
+        <v>0.04728779999999999</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>3.556054219526057</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.1147467658990897</v>
+      </c>
+      <c r="C84">
+        <v>5.491908287535036</v>
+      </c>
+      <c r="D84">
+        <v>18.82878828753504</v>
+      </c>
+      <c r="E84">
+        <v>19.79288</v>
+      </c>
+      <c r="F84">
+        <v>20.07688</v>
+      </c>
+      <c r="G84">
+        <v>6.74</v>
+      </c>
+      <c r="H84">
+        <v>24.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>4.69</v>
+      </c>
+      <c r="K84">
+        <v>0.247</v>
+      </c>
+      <c r="L84">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M84">
+        <v>1.26484344</v>
+      </c>
+      <c r="N84">
+        <v>3.178156560000001</v>
+      </c>
+      <c r="O84">
+        <v>0.7926322460640007</v>
+      </c>
+      <c r="P84">
+        <v>2.385524313936</v>
+      </c>
+      <c r="Q84">
+        <v>2.632524313936</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.422059832772721</v>
+      </c>
+      <c r="T84">
+        <v>6.480288466884467</v>
+      </c>
+      <c r="U84">
+        <v>0.063</v>
+      </c>
+      <c r="V84">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W84">
+        <v>0.04728779999999999</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>3.512687704653787</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.1190386446778346</v>
+      </c>
+      <c r="C85">
+        <v>4.790286021552014</v>
+      </c>
+      <c r="D85">
+        <v>18.37200602155201</v>
+      </c>
+      <c r="E85">
+        <v>20.03772</v>
+      </c>
+      <c r="F85">
+        <v>20.32172</v>
+      </c>
+      <c r="G85">
+        <v>6.74</v>
+      </c>
+      <c r="H85">
+        <v>24.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>4.69</v>
+      </c>
+      <c r="K85">
+        <v>0.247</v>
+      </c>
+      <c r="L85">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M85">
+        <v>1.424552572</v>
+      </c>
+      <c r="N85">
+        <v>3.018447428000001</v>
+      </c>
+      <c r="O85">
+        <v>0.7528007885432008</v>
+      </c>
+      <c r="P85">
+        <v>2.2656466394568</v>
+      </c>
+      <c r="Q85">
+        <v>2.5126466394568</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4433322639872623</v>
+      </c>
+      <c r="T85">
+        <v>6.839970016774234</v>
+      </c>
+      <c r="U85">
+        <v>0.0701</v>
+      </c>
+      <c r="V85">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W85">
+        <v>0.05261705999999999</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>3.11887401513182</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.1189605302565794</v>
+      </c>
+      <c r="C86">
+        <v>4.553561591304305</v>
+      </c>
+      <c r="D86">
+        <v>18.38012159130431</v>
+      </c>
+      <c r="E86">
+        <v>20.28256</v>
+      </c>
+      <c r="F86">
+        <v>20.56656</v>
+      </c>
+      <c r="G86">
+        <v>6.74</v>
+      </c>
+      <c r="H86">
+        <v>24.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>4.69</v>
+      </c>
+      <c r="K86">
+        <v>0.247</v>
+      </c>
+      <c r="L86">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M86">
+        <v>1.441715856</v>
+      </c>
+      <c r="N86">
+        <v>3.001284144</v>
+      </c>
+      <c r="O86">
+        <v>0.7485202655136006</v>
+      </c>
+      <c r="P86">
+        <v>2.2527638784864</v>
+      </c>
+      <c r="Q86">
+        <v>2.4997638784864</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4672637491036211</v>
+      </c>
+      <c r="T86">
+        <v>7.244611760400218</v>
+      </c>
+      <c r="U86">
+        <v>0.0701</v>
+      </c>
+      <c r="V86">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W86">
+        <v>0.05261705999999999</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>3.081744562570726</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.1188824158353242</v>
+      </c>
+      <c r="C87">
+        <v>4.316844334097908</v>
+      </c>
+      <c r="D87">
+        <v>18.38824433409791</v>
+      </c>
+      <c r="E87">
+        <v>20.5274</v>
+      </c>
+      <c r="F87">
+        <v>20.8114</v>
+      </c>
+      <c r="G87">
+        <v>6.74</v>
+      </c>
+      <c r="H87">
+        <v>24.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>4.69</v>
+      </c>
+      <c r="K87">
+        <v>0.247</v>
+      </c>
+      <c r="L87">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M87">
+        <v>1.45887914</v>
+      </c>
+      <c r="N87">
+        <v>2.984120860000001</v>
+      </c>
+      <c r="O87">
+        <v>0.7442397424840007</v>
+      </c>
+      <c r="P87">
+        <v>2.239881117516</v>
+      </c>
+      <c r="Q87">
+        <v>2.486881117516</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4943860989021613</v>
+      </c>
+      <c r="T87">
+        <v>7.703205736509672</v>
+      </c>
+      <c r="U87">
+        <v>0.0701</v>
+      </c>
+      <c r="V87">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W87">
+        <v>0.05261705999999999</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>3.045488744187542</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.118804301414069</v>
+      </c>
+      <c r="C88">
+        <v>4.080134259446989</v>
+      </c>
+      <c r="D88">
+        <v>18.39637425944699</v>
+      </c>
+      <c r="E88">
+        <v>20.77224</v>
+      </c>
+      <c r="F88">
+        <v>21.05624</v>
+      </c>
+      <c r="G88">
+        <v>6.74</v>
+      </c>
+      <c r="H88">
+        <v>24.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>4.69</v>
+      </c>
+      <c r="K88">
+        <v>0.247</v>
+      </c>
+      <c r="L88">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M88">
+        <v>1.476042424</v>
+      </c>
+      <c r="N88">
+        <v>2.966957576</v>
+      </c>
+      <c r="O88">
+        <v>0.7399592194544007</v>
+      </c>
+      <c r="P88">
+        <v>2.2269983565456</v>
+      </c>
+      <c r="Q88">
+        <v>2.4739983565456</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.525383070100493</v>
+      </c>
+      <c r="T88">
+        <v>8.227313137777619</v>
+      </c>
+      <c r="U88">
+        <v>0.0701</v>
+      </c>
+      <c r="V88">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W88">
+        <v>0.05261705999999999</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>3.010076084371407</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.1326355555928138</v>
+      </c>
+      <c r="C89">
+        <v>2.49969722195965</v>
+      </c>
+      <c r="D89">
+        <v>17.06077722195965</v>
+      </c>
+      <c r="E89">
+        <v>21.01708</v>
+      </c>
+      <c r="F89">
+        <v>21.30108</v>
+      </c>
+      <c r="G89">
+        <v>6.74</v>
+      </c>
+      <c r="H89">
+        <v>24.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>4.69</v>
+      </c>
+      <c r="K89">
+        <v>0.247</v>
+      </c>
+      <c r="L89">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M89">
+        <v>1.946918712</v>
+      </c>
+      <c r="N89">
+        <v>2.496081288000001</v>
+      </c>
+      <c r="O89">
+        <v>0.6225226732272006</v>
+      </c>
+      <c r="P89">
+        <v>1.8735586147728</v>
+      </c>
+      <c r="Q89">
+        <v>2.1205586147728</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5611488060985679</v>
+      </c>
+      <c r="T89">
+        <v>8.832052446932941</v>
+      </c>
+      <c r="U89">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V89">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W89">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>2.282067542222071</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.1327173189715586</v>
+      </c>
+      <c r="C90">
+        <v>2.247538201873784</v>
+      </c>
+      <c r="D90">
+        <v>17.05345820187378</v>
+      </c>
+      <c r="E90">
+        <v>21.26192</v>
+      </c>
+      <c r="F90">
+        <v>21.54592</v>
+      </c>
+      <c r="G90">
+        <v>6.74</v>
+      </c>
+      <c r="H90">
+        <v>24.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>4.69</v>
+      </c>
+      <c r="K90">
+        <v>0.247</v>
+      </c>
+      <c r="L90">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M90">
+        <v>1.969297088</v>
+      </c>
+      <c r="N90">
+        <v>2.473702912</v>
+      </c>
+      <c r="O90">
+        <v>0.6169415062528005</v>
+      </c>
+      <c r="P90">
+        <v>1.8567614057472</v>
+      </c>
+      <c r="Q90">
+        <v>2.1037614057472</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6028754980963222</v>
+      </c>
+      <c r="T90">
+        <v>9.537581640947487</v>
+      </c>
+      <c r="U90">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V90">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W90">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>2.256134956515002</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.1327990823503034</v>
+      </c>
+      <c r="C91">
+        <v>1.995385458768588</v>
+      </c>
+      <c r="D91">
+        <v>17.04614545876859</v>
+      </c>
+      <c r="E91">
+        <v>21.50676</v>
+      </c>
+      <c r="F91">
+        <v>21.79076</v>
+      </c>
+      <c r="G91">
+        <v>6.74</v>
+      </c>
+      <c r="H91">
+        <v>24.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>4.69</v>
+      </c>
+      <c r="K91">
+        <v>0.247</v>
+      </c>
+      <c r="L91">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M91">
+        <v>1.991675464</v>
+      </c>
+      <c r="N91">
+        <v>2.451324536</v>
+      </c>
+      <c r="O91">
+        <v>0.6113603392784005</v>
+      </c>
+      <c r="P91">
+        <v>1.8399641967216</v>
+      </c>
+      <c r="Q91">
+        <v>2.0869641967216</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.6521888613663951</v>
+      </c>
+      <c r="T91">
+        <v>10.3713888702374</v>
+      </c>
+      <c r="U91">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V91">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W91">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>2.230785125542924</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.1328808457290483</v>
+      </c>
+      <c r="C92">
+        <v>1.74323898457256</v>
+      </c>
+      <c r="D92">
+        <v>17.03883898457256</v>
+      </c>
+      <c r="E92">
+        <v>21.7516</v>
+      </c>
+      <c r="F92">
+        <v>22.0356</v>
+      </c>
+      <c r="G92">
+        <v>6.74</v>
+      </c>
+      <c r="H92">
+        <v>24.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>4.69</v>
+      </c>
+      <c r="K92">
+        <v>0.247</v>
+      </c>
+      <c r="L92">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M92">
+        <v>2.01405384</v>
+      </c>
+      <c r="N92">
+        <v>2.428946160000001</v>
+      </c>
+      <c r="O92">
+        <v>0.6057791723040006</v>
+      </c>
+      <c r="P92">
+        <v>1.823166987696</v>
+      </c>
+      <c r="Q92">
+        <v>2.070166987696</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.7113648972904829</v>
+      </c>
+      <c r="T92">
+        <v>11.3719575453853</v>
+      </c>
+      <c r="U92">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V92">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W92">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>2.205998624148002</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.1329626091077931</v>
+      </c>
+      <c r="C93">
+        <v>1.491098771228046</v>
+      </c>
+      <c r="D93">
+        <v>17.03153877122804</v>
+      </c>
+      <c r="E93">
+        <v>21.99644</v>
+      </c>
+      <c r="F93">
+        <v>22.28044</v>
+      </c>
+      <c r="G93">
+        <v>6.74</v>
+      </c>
+      <c r="H93">
+        <v>24.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>4.69</v>
+      </c>
+      <c r="K93">
+        <v>0.247</v>
+      </c>
+      <c r="L93">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M93">
+        <v>2.036432216</v>
+      </c>
+      <c r="N93">
+        <v>2.406567784</v>
+      </c>
+      <c r="O93">
+        <v>0.6001980053296005</v>
+      </c>
+      <c r="P93">
+        <v>1.8063697786704</v>
+      </c>
+      <c r="Q93">
+        <v>2.0533697786704</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7836911634199235</v>
+      </c>
+      <c r="T93">
+        <v>12.59487481501051</v>
+      </c>
+      <c r="U93">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V93">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W93">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>2.181756881025497</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.1330443724865379</v>
+      </c>
+      <c r="C94">
+        <v>1.23896481069119</v>
+      </c>
+      <c r="D94">
+        <v>17.02424481069119</v>
+      </c>
+      <c r="E94">
+        <v>22.24128</v>
+      </c>
+      <c r="F94">
+        <v>22.52528</v>
+      </c>
+      <c r="G94">
+        <v>6.74</v>
+      </c>
+      <c r="H94">
+        <v>24.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>4.69</v>
+      </c>
+      <c r="K94">
+        <v>0.247</v>
+      </c>
+      <c r="L94">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M94">
+        <v>2.058810592</v>
+      </c>
+      <c r="N94">
+        <v>2.384189408000001</v>
+      </c>
+      <c r="O94">
+        <v>0.5946168383552005</v>
+      </c>
+      <c r="P94">
+        <v>1.7895725696448</v>
+      </c>
+      <c r="Q94">
+        <v>2.0365725696448</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8740989960817243</v>
+      </c>
+      <c r="T94">
+        <v>14.12352140204202</v>
+      </c>
+      <c r="U94">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V94">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W94">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>2.158042132318698</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.1331261358652827</v>
+      </c>
+      <c r="C95">
+        <v>0.9868370949319143</v>
+      </c>
+      <c r="D95">
+        <v>17.01695709493191</v>
+      </c>
+      <c r="E95">
+        <v>22.48612</v>
+      </c>
+      <c r="F95">
+        <v>22.77012</v>
+      </c>
+      <c r="G95">
+        <v>6.74</v>
+      </c>
+      <c r="H95">
+        <v>24.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>4.69</v>
+      </c>
+      <c r="K95">
+        <v>0.247</v>
+      </c>
+      <c r="L95">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M95">
+        <v>2.081188968</v>
+      </c>
+      <c r="N95">
+        <v>2.361811032</v>
+      </c>
+      <c r="O95">
+        <v>0.5890356713808005</v>
+      </c>
+      <c r="P95">
+        <v>1.7727753606192</v>
+      </c>
+      <c r="Q95">
+        <v>2.0197753606192</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.990337638075468</v>
+      </c>
+      <c r="T95">
+        <v>16.08892415679682</v>
+      </c>
+      <c r="U95">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V95">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W95">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>2.134837378207744</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.1332078992440275</v>
+      </c>
+      <c r="C96">
+        <v>0.734715615933883</v>
+      </c>
+      <c r="D96">
+        <v>17.00967561593388</v>
+      </c>
+      <c r="E96">
+        <v>22.73096</v>
+      </c>
+      <c r="F96">
+        <v>23.01496</v>
+      </c>
+      <c r="G96">
+        <v>6.74</v>
+      </c>
+      <c r="H96">
+        <v>24.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>4.69</v>
+      </c>
+      <c r="K96">
+        <v>0.247</v>
+      </c>
+      <c r="L96">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M96">
+        <v>2.103567344</v>
+      </c>
+      <c r="N96">
+        <v>2.339432656</v>
+      </c>
+      <c r="O96">
+        <v>0.5834545044064006</v>
+      </c>
+      <c r="P96">
+        <v>1.7559781515936</v>
+      </c>
+      <c r="Q96">
+        <v>2.0029781515936</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.145322494067126</v>
+      </c>
+      <c r="T96">
+        <v>18.70946116313656</v>
+      </c>
+      <c r="U96">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V96">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W96">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>2.112126342269364</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.1332896626227723</v>
+      </c>
+      <c r="C97">
+        <v>0.4826003656944735</v>
+      </c>
+      <c r="D97">
+        <v>17.00240036569447</v>
+      </c>
+      <c r="E97">
+        <v>22.9758</v>
+      </c>
+      <c r="F97">
+        <v>23.2598</v>
+      </c>
+      <c r="G97">
+        <v>6.74</v>
+      </c>
+      <c r="H97">
+        <v>24.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>4.69</v>
+      </c>
+      <c r="K97">
+        <v>0.247</v>
+      </c>
+      <c r="L97">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M97">
+        <v>2.12594572</v>
+      </c>
+      <c r="N97">
+        <v>2.31705428</v>
+      </c>
+      <c r="O97">
+        <v>0.5778733374320004</v>
+      </c>
+      <c r="P97">
+        <v>1.739180942568</v>
+      </c>
+      <c r="Q97">
+        <v>1.986180942568</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.362301292455449</v>
+      </c>
+      <c r="T97">
+        <v>22.3782129720122</v>
+      </c>
+      <c r="U97">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V97">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W97">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>2.08989343340337</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.1333714260015172</v>
+      </c>
+      <c r="C98">
+        <v>0.2304913362247483</v>
+      </c>
+      <c r="D98">
+        <v>16.99513133622475</v>
+      </c>
+      <c r="E98">
+        <v>23.22064</v>
+      </c>
+      <c r="F98">
+        <v>23.50464</v>
+      </c>
+      <c r="G98">
+        <v>6.74</v>
+      </c>
+      <c r="H98">
+        <v>24.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>4.69</v>
+      </c>
+      <c r="K98">
+        <v>0.247</v>
+      </c>
+      <c r="L98">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M98">
+        <v>2.148324096</v>
+      </c>
+      <c r="N98">
+        <v>2.294675904</v>
+      </c>
+      <c r="O98">
+        <v>0.5722921704576005</v>
+      </c>
+      <c r="P98">
+        <v>1.7223837335424</v>
+      </c>
+      <c r="Q98">
+        <v>1.9693837335424</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.687769490037928</v>
+      </c>
+      <c r="T98">
+        <v>27.88134068532558</v>
+      </c>
+      <c r="U98">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V98">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W98">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>2.068123710138752</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.133453189380262</v>
+      </c>
+      <c r="C99">
+        <v>-0.02161148045056649</v>
+      </c>
+      <c r="D99">
+        <v>16.98786851954943</v>
+      </c>
+      <c r="E99">
+        <v>23.46548</v>
+      </c>
+      <c r="F99">
+        <v>23.74948</v>
+      </c>
+      <c r="G99">
+        <v>6.74</v>
+      </c>
+      <c r="H99">
+        <v>24.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>4.69</v>
+      </c>
+      <c r="K99">
+        <v>0.247</v>
+      </c>
+      <c r="L99">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M99">
+        <v>2.170702472</v>
+      </c>
+      <c r="N99">
+        <v>2.272297528000001</v>
+      </c>
+      <c r="O99">
+        <v>0.5667110034832006</v>
+      </c>
+      <c r="P99">
+        <v>1.7055865245168</v>
+      </c>
+      <c r="Q99">
+        <v>1.9525865245168</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.230216486008731</v>
+      </c>
+      <c r="T99">
+        <v>37.05322020751463</v>
+      </c>
+      <c r="U99">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V99">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W99">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>2.046802847147631</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.1335349527590068</v>
+      </c>
+      <c r="C100">
+        <v>-0.2737080922931305</v>
+      </c>
+      <c r="D100">
+        <v>16.98061190770687</v>
+      </c>
+      <c r="E100">
+        <v>23.71032</v>
+      </c>
+      <c r="F100">
+        <v>23.99432</v>
+      </c>
+      <c r="G100">
+        <v>6.74</v>
+      </c>
+      <c r="H100">
+        <v>24.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>4.69</v>
+      </c>
+      <c r="K100">
+        <v>0.247</v>
+      </c>
+      <c r="L100">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M100">
+        <v>2.193080848</v>
+      </c>
+      <c r="N100">
+        <v>2.249919152</v>
+      </c>
+      <c r="O100">
+        <v>0.5611298365088004</v>
+      </c>
+      <c r="P100">
+        <v>1.6887893154912</v>
+      </c>
+      <c r="Q100">
+        <v>1.9357893154912</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.315110477950337</v>
+      </c>
+      <c r="T100">
+        <v>55.39697925189274</v>
+      </c>
+      <c r="U100">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V100">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W100">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>2.02591710380939</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.1336167161377516</v>
+      </c>
+      <c r="C101">
+        <v>-0.5257985072510039</v>
+      </c>
+      <c r="D101">
+        <v>16.973361492749</v>
+      </c>
+      <c r="E101">
+        <v>23.95516</v>
+      </c>
+      <c r="F101">
+        <v>24.23916</v>
+      </c>
+      <c r="G101">
+        <v>6.74</v>
+      </c>
+      <c r="H101">
+        <v>24.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>4.69</v>
+      </c>
+      <c r="K101">
+        <v>0.247</v>
+      </c>
+      <c r="L101">
+        <v>4.443000000000001</v>
+      </c>
+      <c r="M101">
+        <v>2.215459224</v>
+      </c>
+      <c r="N101">
+        <v>2.227540776000001</v>
+      </c>
+      <c r="O101">
+        <v>0.5555486695344005</v>
+      </c>
+      <c r="P101">
+        <v>1.6719921064656</v>
+      </c>
+      <c r="Q101">
+        <v>1.9189921064656</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.569792453775157</v>
+      </c>
+      <c r="T101">
+        <v>110.4282563850271</v>
+      </c>
+      <c r="U101">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V101">
+        <v>0.2494000000000002</v>
+      </c>
+      <c r="W101">
+        <v>0.06860483999999999</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>2.005453294680002</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
